--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="17">
-        <v>46177</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="234">
   <si>
     <t>ProductID</t>
   </si>
@@ -1190,6 +1190,9 @@
 - **Table of Specifications**
   - XLSX format
 </t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580685/s2on3kech3iylmxfxawn.jpg, https://res.cloudinary.com/dadubemrv/image/upload/v1771470535/pv600hy73vw3w5yfrdrm.jpg</t>
   </si>
 </sst>
 </file>
@@ -4703,7 +4706,7 @@
         <v>71</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="D29" s="8" t="str">
         <f>CONCATENATE(Sheet2!$D$17, L29, Sheet2!$D$6)</f>

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="238">
   <si>
     <t>ProductID</t>
   </si>
@@ -1192,7 +1192,13 @@
 </t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580685/s2on3kech3iylmxfxawn.jpg, https://res.cloudinary.com/dadubemrv/image/upload/v1771470535/pv600hy73vw3w5yfrdrm.jpg</t>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783262649/xa3ma5xtgdbpiti2pulm.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262653/xelrwfv3qo9fte8tcav5.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262656/erime3c8h1ngvdbdrwdu.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262658/s6wrnagjw7rwy2jvrk9h.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783263602/yd7hsdwqb5dk19s6pakw.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263605/ujoydnhzuhsnv7yic56j.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263608/d8tvcndvdvbcscplmsni.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263611/xnrnsjt720lvbgoycchm.png</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
     <numFmt numFmtId="164" formatCode="mmm\ d"/>
     <numFmt numFmtId="165" formatCode="m\-d\-yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1257,6 +1263,13 @@
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1275,10 +1288,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -1305,8 +1319,15 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4705,7 +4726,7 @@
       <c r="B29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="22" t="s">
         <v>233</v>
       </c>
       <c r="D29" s="8" t="str">
@@ -4825,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="17">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>73</v>
@@ -5477,8 +5498,8 @@
       <c r="B35" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>87</v>
+      <c r="C35" s="23" t="s">
+        <v>234</v>
       </c>
       <c r="D35" s="8" t="str">
         <f>CONCATENATE(Sheet2!$D$17, L35, Sheet2!$D$6)</f>
@@ -5597,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="17">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>88</v>
@@ -14885,52 +14906,51 @@
     <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="C26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
     <hyperlink ref="C27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C35" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C36" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C37" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C38" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C39" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C40" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C41" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C42" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C43" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C47" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C48" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C49" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C50" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C51" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C52" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C53" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C54" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C55" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C56" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C58" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C59" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C60" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C61" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C62" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C63" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C64" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C65" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C66" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C67" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C68" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C69" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C70" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C71" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C72" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C73" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C74" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C75" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C76" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C77" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C78" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C79" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C80" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C81" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C36" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C37" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C38" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C39" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C40" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C41" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C42" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C43" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C47" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C48" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C49" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C51" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C52" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C53" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C55" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C56" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C58" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C59" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C60" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C61" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C62" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C63" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C64" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C65" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C66" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C67" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C68" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C70" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C71" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C72" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C73" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C74" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C75" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C76" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C77" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C78" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C79" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C80" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C81" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C35" r:id="rId70" xr:uid="{D2F92652-BCD8-9046-8224-7D862D4D72B8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <xr:revisionPtr revIDLastSave="0" documentId="11_AD18A7FF5D797A4ED2F3013814DD2D3E1F1A077E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -28,8 +28,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="272">
   <si>
     <t>ProductID</t>
   </si>
@@ -158,87 +180,51 @@
     <t>Grade 10 T3 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G7-T3-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 7 T3 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/TYIT3or.jpeg</t>
   </si>
   <si>
-    <t>G7-T3-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 7 T3 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G7-T3-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 7 T3 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G8-T3-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 8 T3 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/CTCvbDz.jpeg</t>
   </si>
   <si>
-    <t>G8-T3-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 8 T3 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G8-T3-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 8 T3 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G9-T3-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 9 T3 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/c0IwjHZ.jpeg</t>
   </si>
   <si>
-    <t>G9-T3-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 9 T3 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G9-T3-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 9 T3 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G10-T3-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 10 T3 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/PsPVTBV.jpeg</t>
   </si>
   <si>
-    <t>G10-T3-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 10 T3 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G10-T3-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 10 T3 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -251,17 +237,6 @@
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580685/s2on3kech3iylmxfxawn.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">---
-📑 **Competencies Covered**
-- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
-- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
-- Describe and explain the relationships between angle pairs based on their measures.
-- Classify polygons according to the number of sides, whether they are regular or irregular.
-- Classify polygons whether they are convex or non-convex.
-- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
-</t>
-  </si>
-  <si>
     <t>G7-T1-S1-SP</t>
   </si>
   <si>
@@ -304,17 +279,6 @@
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771581041/bwg96ufbzxt2qcdwzb1d.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">---
-📑 **Competencies Covered**
-- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
-- Construct perpendicular and parallel lines.
-- Identify the relationships between angles formed by parallel lines cut by a transversal.
-- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
-- Identify relations that are functions based on the definitions of relations and functions.
-- Determine the domain and range of a function expressed in different representations.
-</t>
-  </si>
-  <si>
     <t>G9-T1-S1-SP</t>
   </si>
   <si>
@@ -348,87 +312,51 @@
     <t>Grade 10 T1 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G7-T1-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 7 T1 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580533/lfmu3tsjv8rrj4tcyhfj.jpg</t>
   </si>
   <si>
-    <t>G7-T1-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 7 T1 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G7-T1-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 7 T1 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G8-T1-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 8 T1 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/Eciazvr.jpeg</t>
   </si>
   <si>
-    <t>G8-T1-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 8 T1 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G8-T1-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 8 T1 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G9-T1-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 9 T1 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580879/sz2yqh5rmfyci6hwivcc.jpg</t>
   </si>
   <si>
-    <t>G9-T1-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 9 T1 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G9-T1-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 9 T1 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G10-T1-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 10 T1 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771581176/bpjq83f63jehupa4mqs7.jpg</t>
   </si>
   <si>
-    <t>G10-T1-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 10 T1 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G10-T1-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 10 T1 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -436,32 +364,6 @@
   </si>
   <si>
     <t>Grade 7 T1 Multiple-Choice Quizzes + Answer Keys</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1770873595/jzt2mkvvxfxztcvqgu3z.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">---
-**Quiz 1.1: Regular and Irregular Polygons** (20 items)
-  - Lesson 1.01: Identifying and Constructing Regular and Irregular Polygons
-  - Lesson 1.02: Drawing Triangles Quadrilaterals and Regular Polygons with Given Angle Measures
-  - Lesson 1.03: Describing and Explaining Relationships Between Angle Pairs
-**Quiz 1.2: Angles and Sides of Polygons** (34 items)  
-  - Lesson 1.04: Classifying Polygons Based on Their Properties
-  - Lesson 1.05: Relationship Between Exterior and Adjacent Interior Angles of a Polygon
-  - Lesson 1.06: Determining Angle Measures and Number of Sides of Polygons
-**Quiz 1.3: Application of Percentages** (30 items)
-  - Lesson 1.07: Solving Problems Involving Percentage Increase and Decrease
-  - Lesson 1.08: Solving Money Problems Involving Percentages
-  - Lesson 1.09: Creating a Financial Plan
-**Quiz 1.4: Uses of Rates** (20 items)
-  - Lesson 1.10: Identifying and Explaining the Uses of Rates
-  - Lesson 1.11: Solving Problems Involving Rates
-  - Lesson 1.12: Describing Rational Numbers as Fractions Decimals or Percentages
-**Quiz 1.5: Rational Numbers** (27 items)
-  - Lesson 1.13: Ordering Rational Numbers on a Number Line
-  - Lesson 1.14: Performing Operations on Rational Numbers
-</t>
   </si>
   <si>
     <t>G8-T1-MQ</t>
@@ -519,30 +421,6 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1770982592/npoqdwippiz4cxvg9bii.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">---
-**Quiz 1.1: Undefined Terms and Basic Geometric Figures** (20 items)
-  - Lesson 1.01: Basic Geometric Figures and Notation
-**Quiz 1.2: Parallel and Perpendicular Lines** (30 items)
-  - Lesson 1.02: Parallel and Perpendicular Lines
-  - Lesson 1.03: Angle Relationships Formed by Parallel Lines and a Transversal
-  - Lesson 1.04: Finding Angle Measures Using Line and Angle Relationships
-**Quiz 1.3: Relations and Functions** (30 items)
-  - Lesson 1.05: Relations and Functions
-  - Lesson 1.06: Domain and Range of Functions
-  - Lesson 1.07: Representing Relationships as Functions
-  - Lesson 1.08.1: Slope and Zeros of Linear Functions from Graphs
-  - Lesson 1.08.2: Slope and Zeros of Linear Functions from Equations
-  - Lesson 1.08.3: Slope and Zeros of Linear Functions from Tables
-**Quiz 1.4: Graphing Linear Functions** (24 items)
-  - Lesson 1.09.1: Graphing Linear Functions and Identifying Domain
-  - Lesson 1.09.2: Graphing Linear Functions and Identifying Range
-  - Lesson 1.09.3: Graphing Linear Functions and Finding Intercepts
-  - Lesson 1.09.4: Graphing Linear Functions and Determining Slope
-  - Lesson 1.10: Linear Models in Real-Life Situations
-  - Lesson 1.11: Solving Problems Involving Linear Functions
-</t>
   </si>
   <si>
     <t>G10-T1-MQ</t>
@@ -659,64 +537,37 @@
     <t>Grade 7 T2 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G8-T2-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 8 T2 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/8n2VCOb.jpeg</t>
   </si>
   <si>
-    <t>G8-T2-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 8 T2 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G8-T2-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 8 T2 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G9-T2-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 9 T2 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/sVIQDun.jpeg</t>
   </si>
   <si>
-    <t>G9-T2-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 9 T2 Periodic Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G9-T2-PT-PP</t>
-  </si>
-  <si>
     <t>Grade 9 T2 Periodic Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
-    <t>G10-T2-PT-BP</t>
-  </si>
-  <si>
     <t>Grade 10 T2 Periodic Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://i.imgur.com/T2J0K9c.jpeg</t>
   </si>
   <si>
-    <t>G10-T2-PT-SP</t>
-  </si>
-  <si>
     <t>Grade 10 T2 Periodic Test + TOS + Answer Key (Standard)</t>
-  </si>
-  <si>
-    <t>G10-T2-PT-PP</t>
   </si>
   <si>
     <t>Grade 10 T2 Periodic Test + TOS + Answer Key (Premium)</t>
@@ -1050,155 +901,401 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
+    <t>Grade 7</t>
+  </si>
+  <si>
+    <t>Grade 8</t>
+  </si>
+  <si>
+    <t>Grade 9</t>
+  </si>
+  <si>
+    <t>Grade 10</t>
+  </si>
+  <si>
+    <t>isPublished</t>
+  </si>
+  <si>
+    <t>1st Term</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/150NUP_Nq2tev-Qn00VInZTAaPrUAssmQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lYVPL8Hz5FbxsfLGVckwDlE6RFrbL0lm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x4fsJFRIZ1vsqPk6OXbzsGErE1XdDNJQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uDaplPaWUxLcLfbi01fHi2bEuRsW5pSy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>2nd Term</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gcw_guW01keoA_5EdpwvtirT8_n3JYfY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19yLqWy-_NCZsNKpVX_CurRsrO0OM4hgZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1by87VOaKncI46lCcnBE-q-OvlVLkMnfW/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10YRHnEQCe2lmZt0moFqzS3qZMP_Kv3lk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>3rd Term</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nHC82ojm3P_QCwT7tUJ4g9cBGDbu1-iM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15fCE2h4hIOibrc0mZOPq-htSd_LXNL0y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ST9ejN8enogNRv9v2qy0w9dwkVxhisbK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13jsRwchCw6wvDtPrbbnMxe6cMPl1Yiy2/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>4th Term</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JTuA7HDdcYP5GODu4ALF6s1lYeTowwD6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZXTfw_Cnny2gO-6a8nTHElyKhlB95m1K/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1BgEtLZ9R7Dr7n-1sIam7OwNUERGgV-E8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OgCeVcpSkbfpJY_0x-13rA8a7xUHGXbS/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783262649/xa3ma5xtgdbpiti2pulm.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262653/xelrwfv3qo9fte8tcav5.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262656/erime3c8h1ngvdbdrwdu.png, 
+https://res.cloudinary.com/dadubemrv/image/upload/v1783262658/s6wrnagjw7rwy2jvrk9h.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783263602/yd7hsdwqb5dk19s6pakw.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263605/ujoydnhzuhsnv7yic56j.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263608/d8tvcndvdvbcscplmsni.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263611/xnrnsjt720lvbgoycchm.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784259489/jon7ha1w9jssifhlph7u.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784259493/l9iore0gcpvw7hcecvvt.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784259496/fyqiathetzwuch9vy3t7.png</t>
+  </si>
+  <si>
+    <t>---
+📑 **Topics Covered**
+**Quiz 1.01.1: Drawing Polygons by Side and Angle Measurements** (35 items)
+  - Lesson 1.01.1: Drawing Regular Polygons by Side and Angle Measurements
+  - Lesson 1.01.2: Drawing Irregular Polygons by Side and Angle Measurements
+  - Lesson 1.01.3: Constructing Triangles, Quadrilaterals, and Regular Polygons
+**Quiz 1.02.1: Relationships Between Angle Pairs** (35 items)  
+  - Lesson 1.02.1: Relationships Between Angle Pairs
+  - Lesson 1.02.2: Classifying Regular and Irregular Polygons
+  - Lesson 1.02.3: Classifying Convex and Non-Convex Polygons
+**Quiz 1.03.1: Exterior and Interior Angles of Polygons** (35 items)
+  - Lesson 1.03.1: Exterior and Interior Angles of Polygons
+  - Lesson 1.03.2: Finding Angle Measures of Polygons
+  - Lesson 1.03.3: Determining the Number of Sides of Polygons
+**Quiz 1.04.1: Percentage Increase and Decrease** (35 items)
+  - Lesson 1.04.1: Percentage Increase
+  - Lesson 1.04.2: Percentage Decrease
+  - Lesson 1.04.3: Money Problems Involving Percentages
+**Quiz 1.05.1: Creating a Financial Plan** (25 items)
+  - Lesson 1.05.1: Creating a Financial Plan
+**Quiz 1.06.1: Understanding Rates** (30 items)
+  - Lesson 1.06.1: Understanding Rates
+  - Lesson 1.06.2: Solving Problems Involving Rates
+**Quiz 1.07.1: Representing Rational Numbers** (35 items)
+  - Lesson 1.07.1: Representing Rational Numbers
+  - Lesson 1.07.2: Ordering Rational Numbers on the Number Line
+**Quiz 1.08.1: Operations on Rational Numbers** (25 items)  
+  - Lesson 1.08.1: Adding Rational Numbers
+  - Lesson 1.08.2: Subtracting Rational Numbers
+  - Lesson 1.09.1: Multiplying Rational Numbers
+  - Lesson 1.09.2: Dividing Rational Numbers
+**Quiz 1.10.1: Square Roots, Cube Roots, and Irrational Numbers** (35 items)
+  - Lesson 1.10.1: Square Roots of Perfect Squares
+  - Lesson 1.10.2: Cube Roots of Perfect Cubes
+  - Lesson 1.10.3: Irrational Numbers and Their Location on the Number Line</t>
+  </si>
+  <si>
+    <t>Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
  - Ready na ang answer key at di ka na magsasagot ng questions. 
  - Masanay ang students sa pagsagot ng multiple choice test. 
- - Parallel ang quiz items sa questions na lalabas sa First Summative test. 
- ---
+ - Parallel ang quiz items sa questions na lalabas sa Summative test at Term Exam. 
+---
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content | </t>
-  </si>
-  <si>
-    <t xml:space="preserve">---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). </t>
-  </si>
-  <si>
-    <t>Grade 7</t>
-  </si>
-  <si>
-    <t>Grade 8</t>
-  </si>
-  <si>
-    <t>Grade 9</t>
-  </si>
-  <si>
-    <t>Grade 10</t>
-  </si>
-  <si>
-    <t>isPublished</t>
-  </si>
-  <si>
-    <t>1st Term</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/150NUP_Nq2tev-Qn00VInZTAaPrUAssmQ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1lYVPL8Hz5FbxsfLGVckwDlE6RFrbL0lm/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1x4fsJFRIZ1vsqPk6OXbzsGErE1XdDNJQ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uDaplPaWUxLcLfbi01fHi2bEuRsW5pSy/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>2nd Term</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gcw_guW01keoA_5EdpwvtirT8_n3JYfY/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/19yLqWy-_NCZsNKpVX_CurRsrO0OM4hgZ/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1by87VOaKncI46lCcnBE-q-OvlVLkMnfW/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10YRHnEQCe2lmZt0moFqzS3qZMP_Kv3lk/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>3rd Term</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nHC82ojm3P_QCwT7tUJ4g9cBGDbu1-iM/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/15fCE2h4hIOibrc0mZOPq-htSd_LXNL0y/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ST9ejN8enogNRv9v2qy0w9dwkVxhisbK/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/13jsRwchCw6wvDtPrbbnMxe6cMPl1Yiy2/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>4th Term</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JTuA7HDdcYP5GODu4ALF6s1lYeTowwD6/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ZXTfw_Cnny2gO-6a8nTHElyKhlB95m1K/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1BgEtLZ9R7Dr7n-1sIam7OwNUERGgV-E8/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1OgCeVcpSkbfpJY_0x-13rA8a7xUHGXbS/view?usp=drivesdk</t>
+| Content |</t>
+  </si>
+  <si>
+    <t>G7-T1-S2-BP</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 Second Summative Test + TOS + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784692768/blzn2f4qf4csagllrdmj.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784692772/mlwmihwoocbpcd5of6rx.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784692776/adpmufdqkz5qxw5yzj0p.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage </t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Product type</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>MQ</t>
+  </si>
+  <si>
+    <t>First Summative test</t>
+  </si>
+  <si>
+    <t>Multiple-choice Quizzes</t>
+  </si>
+  <si>
+    <t>Second Summative test</t>
+  </si>
+  <si>
+    <t>G7-T3-TE-BP</t>
+  </si>
+  <si>
+    <t>G7-T3-TE-SP</t>
+  </si>
+  <si>
+    <t>G7-T3-TE-PP</t>
+  </si>
+  <si>
+    <t>G8-T3-TE-BP</t>
+  </si>
+  <si>
+    <t>G8-T3-TE-SP</t>
+  </si>
+  <si>
+    <t>G8-T3-TE-PP</t>
+  </si>
+  <si>
+    <t>G9-T3-TE-BP</t>
+  </si>
+  <si>
+    <t>G9-T3-TE-SP</t>
+  </si>
+  <si>
+    <t>G9-T3-TE-PP</t>
+  </si>
+  <si>
+    <t>G10-T3-TE-BP</t>
+  </si>
+  <si>
+    <t>G10-T3-TE-SP</t>
+  </si>
+  <si>
+    <t>G10-T3-TE-PP</t>
+  </si>
+  <si>
+    <t>G7-T1-TE-BP</t>
+  </si>
+  <si>
+    <t>G7-T1-TE-SP</t>
+  </si>
+  <si>
+    <t>G7-T1-TE-PP</t>
+  </si>
+  <si>
+    <t>G8-T1-TE-BP</t>
+  </si>
+  <si>
+    <t>G8-T1-TE-SP</t>
+  </si>
+  <si>
+    <t>G8-T1-TE-PP</t>
+  </si>
+  <si>
+    <t>G9-T1-TE-BP</t>
+  </si>
+  <si>
+    <t>G9-T1-TE-SP</t>
+  </si>
+  <si>
+    <t>G9-T1-TE-PP</t>
+  </si>
+  <si>
+    <t>G10-T1-TE-BP</t>
+  </si>
+  <si>
+    <t>G10-T1-TE-SP</t>
+  </si>
+  <si>
+    <t>G10-T1-TE-PP</t>
+  </si>
+  <si>
+    <t>G8-T2-TE-BP</t>
+  </si>
+  <si>
+    <t>G8-T2-TE-SP</t>
+  </si>
+  <si>
+    <t>G8-T2-TE-PP</t>
+  </si>
+  <si>
+    <t>G9-T2-TE-BP</t>
+  </si>
+  <si>
+    <t>G9-T2-TE-SP</t>
+  </si>
+  <si>
+    <t>G9-T2-TE-PP</t>
+  </si>
+  <si>
+    <t>G10-T2-TE-BP</t>
+  </si>
+  <si>
+    <t>G10-T2-TE-SP</t>
+  </si>
+  <si>
+    <t>G10-T2-TE-PP</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>Term Exam</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>First Term</t>
+  </si>
+  <si>
+    <t>Second Term</t>
+  </si>
+  <si>
+    <t>Third Term</t>
+  </si>
+  <si>
+    <t>Grade level</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>Package type</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>Basic Assessment Package</t>
+  </si>
+  <si>
+    <t>Standard Assessment Package</t>
+  </si>
+  <si>
+    <t>Premium Assessment Package</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Items</t>
   </si>
   <si>
     <t>ST Regular Basic</t>
   </si>
   <si>
-    <t xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: 15 days  
-- 25-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 25-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
-</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783262649/xa3ma5xtgdbpiti2pulm.png, 
-https://res.cloudinary.com/dadubemrv/image/upload/v1783262653/xelrwfv3qo9fte8tcav5.png, 
-https://res.cloudinary.com/dadubemrv/image/upload/v1783262656/erime3c8h1ngvdbdrwdu.png, 
-https://res.cloudinary.com/dadubemrv/image/upload/v1783262658/s6wrnagjw7rwy2jvrk9h.png</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1783263602/yd7hsdwqb5dk19s6pakw.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263605/ujoydnhzuhsnv7yic56j.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263608/d8tvcndvdvbcscplmsni.png,https://res.cloudinary.com/dadubemrv/image/upload/v1783263611/xnrnsjt720lvbgoycchm.png</t>
+    <t>G9-T1-S2-BP</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 Second Summative Test + TOS + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784731784/ptqhzxe6hdaphiivprrc.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784731787/jc6dwnedukuiwimgdgxv.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784731789/aidqozqvzsxtxmtppi1c.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+---
+📑 **Competencies Covered**
+- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
+- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
+- Describe and explain the relationships between angle pairs based on their measures.
+- Classify polygons according to the number of sides, whether they are regular or irregular.
+- Classify polygons whether they are convex or non-convex.
+- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+---
+📑 **Competencies Covered**
+- Determine the measures of angles of polygons.
+- Determine the number of sides of polygons.
+- Solve problems involving percentage increase and percentage decrease.
+- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
+- Create a financial plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+---
+📑 **Competencies Covered**
+- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
+- Construct perpendicular and parallel lines.
+- Identify the relationships between angles formed by parallel lines cut by a transversal.
+- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
+- Identify relations that are functions based on the definitions of relations and functions.
+- Determine the domain and range of a function expressed in different representations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+---
+📑 **Competencies Covered**
+- Express the relationship between two variables as a function.
+- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
+- Graph a linear function and determine its domain, range, intercepts, and slope.
+- Represent linear relationships found in real-life situations using different representations.
+- Solve problems involving linear functions.
+- Determine conditions that guarantee parallelism and perpendicularity of lines.</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1389,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -1325,6 +1422,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1544,7 +1652,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB982"/>
+  <dimension ref="A1:AB984"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
@@ -1580,6 +1688,27 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" t="s">
+        <v>243</v>
+      </c>
+      <c r="O1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>262</v>
+      </c>
+      <c r="R1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3201,13 +3330,13 @@
     </row>
     <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="C16" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>44</v>
       </c>
       <c r="D16" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -3336,13 +3465,13 @@
     </row>
     <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -3458,13 +3587,13 @@
     </row>
     <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -3580,13 +3709,13 @@
     </row>
     <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -3715,13 +3844,13 @@
     </row>
     <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D20" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -3837,13 +3966,13 @@
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13" t="s">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -3959,13 +4088,13 @@
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D22" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -4094,13 +4223,13 @@
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D23" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -4216,13 +4345,13 @@
     </row>
     <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D24" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -4338,13 +4467,13 @@
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13" t="s">
-        <v>63</v>
+        <v>217</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -4473,13 +4602,13 @@
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D26" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -4595,13 +4724,13 @@
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D27" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -4720,18 +4849,50 @@
       <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>71</v>
+      <c r="A29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$D$17, L29, Sheet2!$D$6)</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M29, " mo, ",Sheet1!O29," KasaMath? Kuha ka na ng ", Sheet1!P29,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P29,"?**
+",Sheet2!D$17, L29, _xlfn._LONGTEXT("
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+M","ag-send ka lang ng ₱"),Sheet1!F29," para sa **", Sheet1!M29,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R29,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 7 KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
 - Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
@@ -4745,6 +4906,14 @@
 [![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
 *Sample TOS formatted using 21st Century Skills*
 ---
+📑 **Competencies Covered**
+- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
+- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
+- Describe and explain the relationships between angle pairs based on their measures.
+- Classify polygons according to the number of sides, whether they are regular or irregular.
+- Classify polygons whether they are convex or non-convex.
+- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
+---
 ## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
 - Name:
 - Email address:
@@ -4756,7 +4925,7 @@
 ---
 ## Step 2: Payment and Delivery
 ### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. 
+Mag-send ka lang ng ₱60 para sa **First Summative test**. 
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
@@ -4775,17 +4944,9 @@
 - **Table of Specifications**
   - XLSX format
 ---
-📑 **Competencies Covered**
-- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
-- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
-- Describe and explain the relationships between angle pairs based on their measures.
-- Classify polygons according to the number of sides, whether they are regular or irregular.
-- Classify polygons whether they are convex or non-convex.
-- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). </v>
-      </c>
-      <c r="E29" s="4" t="str">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E29" s="10" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -4831,32 +4992,48 @@
 </v>
       </c>
       <c r="F29" s="9">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G29" s="9">
-        <v>84</v>
-      </c>
-      <c r="H29" s="4" t="b">
+        <v>50</v>
+      </c>
+      <c r="H29" s="10" t="b">
         <v>0</v>
       </c>
       <c r="I29" s="5">
         <v>46176</v>
       </c>
-      <c r="J29" s="4" t="b">
+      <c r="J29" s="10" t="b">
         <v>1</v>
       </c>
       <c r="K29" s="17">
         <v>46179</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+      <c r="L29" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="M29" s="10" t="str" cm="1">
+        <f t="array" ref="M29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A29)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N29" s="10" t="str" cm="1">
+        <f t="array" ref="N29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A29)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O29" s="10" t="str" cm="1">
+        <f t="array" ref="O29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A29)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P29" s="10" t="str" cm="1">
+        <f t="array" ref="P29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A29)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>15</v>
+      </c>
+      <c r="R29" s="10">
+        <v>25</v>
+      </c>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
       <c r="U29" s="10"/>
@@ -4868,17 +5045,213 @@
       <c r="AA29" s="10"/>
       <c r="AB29" s="10"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>72</v>
+    <row r="30" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>198</v>
       </c>
       <c r="D30" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M30, " mo, ",Sheet1!O30," KasaMath? Kuha ka na ng ", Sheet1!P30,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P30,"?**
+",Sheet2!D$17, L30, _xlfn._LONGTEXT("
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+M","ag-send ka lang ng ₱"),Sheet1!F30," para sa **", Sheet1!M30,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R30,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 7 KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Table of Specifications (21st Century format)  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Determine the measures of angles of polygons.
+- Determine the number of sides of polygons.
+- Solve problems involving percentage increase and percentage decrease.
+- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
+- Create a financial plan.
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱60 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f>Sheet2!$A$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Tipid din sa budget dahil naka-**30% discount**.
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications (Bloom’s Taxonomy format)  
+- Number of days: 35 days  
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="F30" s="9">
+        <v>60</v>
+      </c>
+      <c r="G30" s="9">
+        <v>50</v>
+      </c>
+      <c r="H30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L30" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="M30" s="10" t="str" cm="1">
+        <f t="array" ref="M30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A30)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N30" s="10" t="str" cm="1">
+        <f t="array" ref="N30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A30)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O30" s="10" t="str" cm="1">
+        <f t="array" ref="O30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A30)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P30" s="10" t="str" cm="1">
+        <f t="array" ref="P30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A30)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>15</v>
+      </c>
+      <c r="R30" s="10">
+        <v>25</v>
+      </c>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AA30" s="10"/>
+      <c r="AB30" s="10"/>
+    </row>
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -4924,7 +5297,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E30" s="4" t="str">
+      <c r="E31" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -4971,36 +5344,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F30" s="15">
+      <c r="F31" s="15">
         <v>165</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G31" s="15">
         <v>115</v>
       </c>
-      <c r="H30" s="4" t="b">
+      <c r="H31" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I31" s="5">
         <v>46176</v>
       </c>
-      <c r="J30" s="4" t="b">
+      <c r="J31" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K31" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="8" t="str">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5046,7 +5419,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E31" s="4" t="str">
+      <c r="E32" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5093,36 +5466,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F31" s="15">
+      <c r="F32" s="15">
         <v>350</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G32" s="15">
         <v>245</v>
       </c>
-      <c r="H31" s="4" t="b">
+      <c r="H32" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I32" s="5">
         <v>46176</v>
       </c>
-      <c r="J31" s="4" t="b">
+      <c r="J32" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K32" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="8" t="str">
+    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5166,7 +5539,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E32" s="4" t="str">
+      <c r="E33" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5211,53 +5584,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F32" s="9">
+      <c r="F33" s="9">
         <v>120</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G33" s="9">
         <v>84</v>
       </c>
-      <c r="H32" s="4" t="b">
+      <c r="H33" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I33" s="5">
         <v>46176</v>
       </c>
-      <c r="J32" s="4" t="b">
+      <c r="J33" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K33" s="17">
         <v>46176</v>
       </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="10"/>
-      <c r="AB32" s="10"/>
-    </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="8" t="str">
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
+    </row>
+    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5303,7 +5676,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E33" s="4" t="str">
+      <c r="E34" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5350,36 +5723,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F33" s="15">
+      <c r="F34" s="15">
         <v>165</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G34" s="15">
         <v>115</v>
       </c>
-      <c r="H33" s="4" t="b">
+      <c r="H34" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I34" s="5">
         <v>46176</v>
       </c>
-      <c r="J33" s="4" t="b">
+      <c r="J34" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K34" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="8" t="str">
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5425,7 +5798,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E34" s="4" t="str">
+      <c r="E35" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5472,38 +5845,70 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F34" s="15">
+      <c r="F35" s="15">
         <v>350</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G35" s="15">
         <v>245</v>
       </c>
-      <c r="H34" s="4" t="b">
+      <c r="H35" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I35" s="5">
         <v>46176</v>
       </c>
-      <c r="J34" s="4" t="b">
+      <c r="J35" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K35" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="D35" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$D$17, L35, Sheet2!$D$6)</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M36, " mo, ",Sheet1!O36," KasaMath? Kuha ka na ng ", Sheet1!P36,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P36,"?**
+",Sheet2!D$17, L36, _xlfn._LONGTEXT("
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+M","ag-send ka lang ng ₱"),Sheet1!F36," para sa **", Sheet1!M36,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R36,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
 - Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
@@ -5517,6 +5922,14 @@
 [![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
 *Sample TOS formatted using 21st Century Skills*
 ---
+📑 **Competencies Covered**
+- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
+- Construct perpendicular and parallel lines.
+- Identify the relationships between angles formed by parallel lines cut by a transversal.
+- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
+- Identify relations that are functions based on the definitions of relations and functions.
+- Determine the domain and range of a function expressed in different representations.
+---
 ## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
 - Name:
 - Email address:
@@ -5528,7 +5941,7 @@
 ---
 ## Step 2: Payment and Delivery
 ### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. 
+Mag-send ka lang ng ₱60 para sa **First Summative test**. 
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
@@ -5547,17 +5960,9 @@
 - **Table of Specifications**
   - XLSX format
 ---
-📑 **Competencies Covered**
-- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
-- Construct perpendicular and parallel lines.
-- Identify the relationships between angles formed by parallel lines cut by a transversal.
-- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
-- Identify relations that are functions based on the definitions of relations and functions.
-- Determine the domain and range of a function expressed in different representations.
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). </v>
-      </c>
-      <c r="E35" s="4" t="str">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E36" s="10" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5602,55 +6007,268 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F35" s="9">
-        <v>120</v>
-      </c>
-      <c r="G35" s="9">
-        <v>84</v>
-      </c>
-      <c r="H35" s="4" t="b">
+      <c r="F36" s="9">
+        <v>60</v>
+      </c>
+      <c r="G36" s="9">
+        <v>50</v>
+      </c>
+      <c r="H36" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I36" s="5">
         <v>46176</v>
       </c>
-      <c r="J35" s="4" t="b">
+      <c r="J36" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K36" s="17">
         <v>46179</v>
       </c>
-      <c r="L35" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="10"/>
-      <c r="Y35" s="10"/>
-      <c r="Z35" s="10"/>
-      <c r="AA35" s="10"/>
-      <c r="AB35" s="10"/>
-    </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="8" t="str">
+      <c r="L36" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="M36" s="10" t="str" cm="1">
+        <f t="array" ref="M36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A36)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N36" s="10" t="str" cm="1">
+        <f t="array" ref="N36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A36)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O36" s="10" t="str" cm="1">
+        <f t="array" ref="O36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A36)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P36" s="10" t="str" cm="1">
+        <f t="array" ref="P36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A36)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>15</v>
+      </c>
+      <c r="R36" s="10">
+        <v>25</v>
+      </c>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+      <c r="AA36" s="10"/>
+      <c r="AB36" s="10"/>
+    </row>
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D37" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M37, " mo, ",Sheet1!O37," KasaMath? Kuha ka na ng ", Sheet1!P37,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P37,"?**
+",Sheet2!D$17, L37, _xlfn._LONGTEXT("
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+M","ag-send ka lang ng ₱"),Sheet1!F37," para sa **", Sheet1!M37,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R37,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Table of Specifications (21st Century format)  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Express the relationship between two variables as a function.
+- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
+- Graph a linear function and determine its domain, range, intercepts, and slope.
+- Represent linear relationships found in real-life situations using different representations.
+- Solve problems involving linear functions.
+- Determine conditions that guarantee parallelism and perpendicularity of lines.
+---
+## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
+- Name:
+- Email address:
+- Grade level:
+- Region:
+- Division:
+- Name of School:
+- Address of School:
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱60 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E37" s="4" t="str">
+        <f>Sheet2!$A$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Tipid din sa budget dahil naka-**30% discount**.
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications (Bloom’s Taxonomy format)  
+- Number of days: 35 days  
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="F37" s="9">
+        <v>60</v>
+      </c>
+      <c r="G37" s="9">
+        <v>50</v>
+      </c>
+      <c r="H37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L37" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="M37" s="10" t="str" cm="1">
+        <f t="array" ref="M37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A37)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N37" s="10" t="str" cm="1">
+        <f t="array" ref="N37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A37)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O37" s="10" t="str" cm="1">
+        <f t="array" ref="O37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A37)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P37" s="10" t="str" cm="1">
+        <f t="array" ref="P37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A37)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>15</v>
+      </c>
+      <c r="R37" s="10">
+        <v>25</v>
+      </c>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+      <c r="AA37" s="10"/>
+      <c r="AB37" s="10"/>
+    </row>
+    <row r="38" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5696,7 +6314,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E36" s="4" t="str">
+      <c r="E38" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5743,36 +6361,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F36" s="15">
+      <c r="F38" s="15">
         <v>165</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G38" s="15">
         <v>115</v>
       </c>
-      <c r="H36" s="4" t="b">
+      <c r="H38" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I38" s="5">
         <v>46176</v>
       </c>
-      <c r="J36" s="4" t="b">
+      <c r="J38" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K36" s="17">
+      <c r="K38" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="8" t="str">
+    <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5818,7 +6436,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E37" s="4" t="str">
+      <c r="E39" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5865,36 +6483,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F37" s="15">
+      <c r="F39" s="15">
         <v>350</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G39" s="15">
         <v>245</v>
       </c>
-      <c r="H37" s="4" t="b">
+      <c r="H39" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I39" s="5">
         <v>46176</v>
       </c>
-      <c r="J37" s="4" t="b">
+      <c r="J39" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K39" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="8" t="str">
+    <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5938,7 +6556,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E38" s="4" t="str">
+      <c r="E40" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5983,53 +6601,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F38" s="9">
+      <c r="F40" s="9">
         <v>120</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G40" s="9">
         <v>84</v>
       </c>
-      <c r="H38" s="4" t="b">
+      <c r="H40" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I40" s="5">
         <v>46176</v>
       </c>
-      <c r="J38" s="4" t="b">
+      <c r="J40" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K38" s="17">
+      <c r="K40" s="17">
         <v>46176</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10"/>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10"/>
-      <c r="AB38" s="10"/>
-    </row>
-    <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="8" t="str">
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
+      <c r="AA40" s="10"/>
+      <c r="AB40" s="10"/>
+    </row>
+    <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6075,7 +6693,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E39" s="4" t="str">
+      <c r="E41" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6122,36 +6740,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F39" s="15">
+      <c r="F41" s="15">
         <v>165</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G41" s="15">
         <v>115</v>
       </c>
-      <c r="H39" s="4" t="b">
+      <c r="H41" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I41" s="5">
         <v>46176</v>
       </c>
-      <c r="J39" s="4" t="b">
+      <c r="J41" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K41" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="8" t="str">
+    <row r="42" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6197,7 +6815,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E40" s="4" t="str">
+      <c r="E42" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6244,36 +6862,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F40" s="15">
+      <c r="F42" s="15">
         <v>350</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G42" s="15">
         <v>245</v>
       </c>
-      <c r="H40" s="4" t="b">
+      <c r="H42" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I42" s="5">
         <v>46176</v>
       </c>
-      <c r="J40" s="4" t="b">
+      <c r="J42" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K40" s="17">
+      <c r="K42" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" s="8" t="str">
+    <row r="43" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6317,7 +6935,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E41" s="4" t="str">
+      <c r="E43" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6362,53 +6980,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F41" s="9">
+      <c r="F43" s="9">
         <v>120</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G43" s="9">
         <v>84</v>
       </c>
-      <c r="H41" s="4" t="b">
+      <c r="H43" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I43" s="5">
         <v>46176</v>
       </c>
-      <c r="J41" s="4" t="b">
+      <c r="J43" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K41" s="17">
+      <c r="K43" s="17">
         <v>46176</v>
       </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="10"/>
-      <c r="Y41" s="10"/>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="10"/>
-      <c r="AB41" s="10"/>
-    </row>
-    <row r="42" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" s="8" t="str">
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
+      <c r="Z43" s="10"/>
+      <c r="AA43" s="10"/>
+      <c r="AB43" s="10"/>
+    </row>
+    <row r="44" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6454,7 +7072,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E42" s="4" t="str">
+      <c r="E44" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6501,36 +7119,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F42" s="15">
+      <c r="F44" s="15">
         <v>165</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G44" s="15">
         <v>115</v>
       </c>
-      <c r="H42" s="4" t="b">
+      <c r="H44" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I44" s="5">
         <v>46176</v>
       </c>
-      <c r="J42" s="4" t="b">
+      <c r="J44" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K42" s="17">
+      <c r="K44" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="8" t="str">
+    <row r="45" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6576,7 +7194,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E43" s="4" t="str">
+      <c r="E45" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6623,36 +7241,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F43" s="15">
+      <c r="F45" s="15">
         <v>350</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G45" s="15">
         <v>245</v>
       </c>
-      <c r="H43" s="4" t="b">
+      <c r="H45" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I45" s="5">
         <v>46176</v>
       </c>
-      <c r="J43" s="4" t="b">
+      <c r="J45" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K43" s="17">
+      <c r="K45" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" s="8" t="str">
+    <row r="46" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6696,7 +7314,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E44" s="4" t="str">
+      <c r="E46" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6741,53 +7359,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F44" s="9">
+      <c r="F46" s="9">
         <v>120</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G46" s="9">
         <v>84</v>
       </c>
-      <c r="H44" s="4" t="b">
+      <c r="H46" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I46" s="5">
         <v>46176</v>
       </c>
-      <c r="J44" s="4" t="b">
+      <c r="J46" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K44" s="17">
+      <c r="K46" s="17">
         <v>46176</v>
       </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10"/>
-      <c r="T44" s="10"/>
-      <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-      <c r="Y44" s="10"/>
-      <c r="Z44" s="10"/>
-      <c r="AA44" s="10"/>
-      <c r="AB44" s="10"/>
-    </row>
-    <row r="45" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" s="8" t="str">
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
+      <c r="Z46" s="10"/>
+      <c r="AA46" s="10"/>
+      <c r="AB46" s="10"/>
+    </row>
+    <row r="47" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6833,7 +7451,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E45" s="4" t="str">
+      <c r="E47" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6880,36 +7498,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F45" s="15">
+      <c r="F47" s="15">
         <v>165</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G47" s="15">
         <v>115</v>
       </c>
-      <c r="H45" s="4" t="b">
+      <c r="H47" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I47" s="5">
         <v>46176</v>
       </c>
-      <c r="J45" s="4" t="b">
+      <c r="J47" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K45" s="17">
+      <c r="K47" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" s="8" t="str">
+    <row r="48" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6955,7 +7573,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E46" s="4" t="str">
+      <c r="E48" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7002,36 +7620,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F46" s="15">
+      <c r="F48" s="15">
         <v>350</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G48" s="15">
         <v>245</v>
       </c>
-      <c r="H46" s="4" t="b">
+      <c r="H48" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I48" s="5">
         <v>46176</v>
       </c>
-      <c r="J46" s="4" t="b">
+      <c r="J48" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K46" s="17">
+      <c r="K48" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="8" t="str">
+    <row r="49" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -7075,7 +7693,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E47" s="4" t="str">
+      <c r="E49" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -7120,53 +7738,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F47" s="9">
+      <c r="F49" s="9">
         <v>120</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G49" s="9">
         <v>84</v>
       </c>
-      <c r="H47" s="4" t="b">
+      <c r="H49" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I49" s="5">
         <v>46176</v>
       </c>
-      <c r="J47" s="4" t="b">
+      <c r="J49" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K47" s="17">
+      <c r="K49" s="17">
         <v>46176</v>
       </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10"/>
-      <c r="X47" s="10"/>
-      <c r="Y47" s="10"/>
-      <c r="Z47" s="10"/>
-      <c r="AA47" s="10"/>
-      <c r="AB47" s="10"/>
-    </row>
-    <row r="48" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="8" t="str">
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
+      <c r="Y49" s="10"/>
+      <c r="Z49" s="10"/>
+      <c r="AA49" s="10"/>
+      <c r="AB49" s="10"/>
+    </row>
+    <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7212,7 +7830,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E48" s="4" t="str">
+      <c r="E50" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7259,36 +7877,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F48" s="15">
+      <c r="F50" s="15">
         <v>165</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G50" s="15">
         <v>115</v>
       </c>
-      <c r="H48" s="4" t="b">
+      <c r="H50" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I50" s="5">
         <v>46176</v>
       </c>
-      <c r="J48" s="4" t="b">
+      <c r="J50" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K48" s="17">
+      <c r="K50" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D49" s="8" t="str">
+    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7334,7 +7952,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E49" s="4" t="str">
+      <c r="E51" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7381,36 +7999,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F49" s="15">
+      <c r="F51" s="15">
         <v>350</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G51" s="15">
         <v>245</v>
       </c>
-      <c r="H49" s="4" t="b">
+      <c r="H51" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I51" s="5">
         <v>46176</v>
       </c>
-      <c r="J49" s="4" t="b">
+      <c r="J51" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K49" s="17">
+      <c r="K51" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" s="8" t="str">
+    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -7454,7 +8072,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E50" s="4" t="str">
+      <c r="E52" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -7499,53 +8117,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F50" s="9">
+      <c r="F52" s="9">
         <v>120</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G52" s="9">
         <v>84</v>
       </c>
-      <c r="H50" s="4" t="b">
+      <c r="H52" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I52" s="5">
         <v>46176</v>
       </c>
-      <c r="J50" s="4" t="b">
+      <c r="J52" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K50" s="17">
+      <c r="K52" s="17">
         <v>46176</v>
       </c>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="10"/>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-      <c r="Y50" s="10"/>
-      <c r="Z50" s="10"/>
-      <c r="AA50" s="10"/>
-      <c r="AB50" s="10"/>
-    </row>
-    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="8" t="str">
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
+      <c r="X52" s="10"/>
+      <c r="Y52" s="10"/>
+      <c r="Z52" s="10"/>
+      <c r="AA52" s="10"/>
+      <c r="AB52" s="10"/>
+    </row>
+    <row r="53" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7591,7 +8209,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E51" s="4" t="str">
+      <c r="E53" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7638,36 +8256,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F51" s="15">
+      <c r="F53" s="15">
         <v>165</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G53" s="15">
         <v>115</v>
       </c>
-      <c r="H51" s="4" t="b">
+      <c r="H53" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I53" s="5">
         <v>46176</v>
       </c>
-      <c r="J51" s="4" t="b">
+      <c r="J53" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K51" s="17">
+      <c r="K53" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="8" t="str">
+    <row r="54" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7713,7 +8331,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E52" s="4" t="str">
+      <c r="E54" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7760,78 +8378,93 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F52" s="15">
+      <c r="F54" s="15">
         <v>350</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G54" s="15">
         <v>245</v>
       </c>
-      <c r="H52" s="4" t="b">
+      <c r="H54" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I54" s="5">
         <v>46176</v>
       </c>
-      <c r="J52" s="4" t="b">
+      <c r="J54" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K52" s="17">
+      <c r="K54" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F53/25," Multiple-choice Quizzes |
+    <row r="55" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F55/10," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H53, G53, F53),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A53), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L53, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+| Price | ₱",IF(H55, G55, F55),"|", CHAR(10), CHAR(10),CHAR(10), L55, CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A55), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
         <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
  - Ready na ang answer key at di ka na magsasagot ng questions. 
  - Masanay ang students sa pagsagot ng multiple choice test. 
- - Parallel ang quiz items sa questions na lalabas sa First Summative test. 
- ---
+ - Parallel ang quiz items sa questions na lalabas sa Summative test at Term Exam. 
+---
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content | 5 Multiple-choice Quizzes |
+| Content |9 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱125|
+| Price | ₱90|
+---
+📑 **Topics Covered**
+**Quiz 1.01.1: Drawing Polygons by Side and Angle Measurements** (35 items)
+  - Lesson 1.01.1: Drawing Regular Polygons by Side and Angle Measurements
+  - Lesson 1.01.2: Drawing Irregular Polygons by Side and Angle Measurements
+  - Lesson 1.01.3: Constructing Triangles, Quadrilaterals, and Regular Polygons
+**Quiz 1.02.1: Relationships Between Angle Pairs** (35 items)  
+  - Lesson 1.02.1: Relationships Between Angle Pairs
+  - Lesson 1.02.2: Classifying Regular and Irregular Polygons
+  - Lesson 1.02.3: Classifying Convex and Non-Convex Polygons
+**Quiz 1.03.1: Exterior and Interior Angles of Polygons** (35 items)
+  - Lesson 1.03.1: Exterior and Interior Angles of Polygons
+  - Lesson 1.03.2: Finding Angle Measures of Polygons
+  - Lesson 1.03.3: Determining the Number of Sides of Polygons
+**Quiz 1.04.1: Percentage Increase and Decrease** (35 items)
+  - Lesson 1.04.1: Percentage Increase
+  - Lesson 1.04.2: Percentage Decrease
+  - Lesson 1.04.3: Money Problems Involving Percentages
+**Quiz 1.05.1: Creating a Financial Plan** (25 items)
+  - Lesson 1.05.1: Creating a Financial Plan
+**Quiz 1.06.1: Understanding Rates** (30 items)
+  - Lesson 1.06.1: Understanding Rates
+  - Lesson 1.06.2: Solving Problems Involving Rates
+**Quiz 1.07.1: Representing Rational Numbers** (35 items)
+  - Lesson 1.07.1: Representing Rational Numbers
+  - Lesson 1.07.2: Ordering Rational Numbers on the Number Line
+**Quiz 1.08.1: Operations on Rational Numbers** (25 items)  
+  - Lesson 1.08.1: Adding Rational Numbers
+  - Lesson 1.08.2: Subtracting Rational Numbers
+  - Lesson 1.09.1: Multiplying Rational Numbers
+  - Lesson 1.09.2: Dividing Rational Numbers
+**Quiz 1.10.1: Square Roots, Cube Roots, and Irrational Numbers** (35 items)
+  - Lesson 1.10.1: Square Roots of Perfect Squares
+  - Lesson 1.10.2: Cube Roots of Perfect Cubes
+  - Lesson 1.10.3: Irrational Numbers and Their Location on the Number Line
 ---
 📥 **I-fill out ang Order Form**
 {{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-mq" height="850" &gt;}}
----
-**Quiz 1.1: Regular and Irregular Polygons** (20 items)
-  - Lesson 1.01: Identifying and Constructing Regular and Irregular Polygons
-  - Lesson 1.02: Drawing Triangles Quadrilaterals and Regular Polygons with Given Angle Measures
-  - Lesson 1.03: Describing and Explaining Relationships Between Angle Pairs
-**Quiz 1.2: Angles and Sides of Polygons** (34 items)  
-  - Lesson 1.04: Classifying Polygons Based on Their Properties
-  - Lesson 1.05: Relationship Between Exterior and Adjacent Interior Angles of a Polygon
-  - Lesson 1.06: Determining Angle Measures and Number of Sides of Polygons
-**Quiz 1.3: Application of Percentages** (30 items)
-  - Lesson 1.07: Solving Problems Involving Percentage Increase and Decrease
-  - Lesson 1.08: Solving Money Problems Involving Percentages
-  - Lesson 1.09: Creating a Financial Plan
-**Quiz 1.4: Uses of Rates** (20 items)
-  - Lesson 1.10: Identifying and Explaining the Uses of Rates
-  - Lesson 1.11: Solving Problems Involving Rates
-  - Lesson 1.12: Describing Rational Numbers as Fractions Decimals or Percentages
-**Quiz 1.5: Rational Numbers** (27 items)
-  - Lesson 1.13: Ordering Rational Numbers on a Number Line
-  - Lesson 1.14: Performing Operations on Rational Numbers
 ---
 🛒 **Payment Methods**
 | Method | Account Details | Payment Amount |
@@ -7848,70 +8481,72 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
 </v>
       </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="9">
-        <v>125</v>
-      </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="4" t="b">
+      <c r="E55" s="4"/>
+      <c r="F55" s="9">
+        <v>90</v>
+      </c>
+      <c r="G55" s="9">
+        <v>80</v>
+      </c>
+      <c r="H55" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I55" s="5">
         <v>46176</v>
       </c>
-      <c r="J53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" s="17">
+      <c r="J55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" s="17">
         <v>46176</v>
       </c>
-      <c r="L53" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
-      <c r="AA53" s="10"/>
-      <c r="AB53" s="10"/>
-    </row>
-    <row r="54" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D54" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F54/25," Multiple-choice Quizzes |
+      <c r="L55" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
+      <c r="V55" s="10"/>
+      <c r="W55" s="10"/>
+      <c r="X55" s="10"/>
+      <c r="Y55" s="10"/>
+      <c r="Z55" s="10"/>
+      <c r="AA55" s="10"/>
+      <c r="AB55" s="10"/>
+    </row>
+    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F56/25," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H54, G54, F54),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A54), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L54, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+| Price | ₱",IF(H56, G56, F56),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A56), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L56, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
         <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
  - Ready na ang answer key at di ka na magsasagot ng questions. 
  - Masanay ang students sa pagsagot ng multiple choice test. 
- - Parallel ang quiz items sa questions na lalabas sa First Summative test. 
- ---
+ - Parallel ang quiz items sa questions na lalabas sa Summative test at Term Exam. 
+---
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content | 6 Multiple-choice Quizzes |
+| Content |6 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
 | Price | ₱150|
@@ -7970,97 +8605,76 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
 </v>
       </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="9">
+      <c r="E56" s="4"/>
+      <c r="F56" s="9">
         <v>150</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="4" t="b">
+      <c r="G56" s="9"/>
+      <c r="H56" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I56" s="5">
         <v>46176</v>
       </c>
-      <c r="J54" s="4" t="b">
+      <c r="J56" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K54" s="17">
+      <c r="K56" s="17">
         <v>46176</v>
       </c>
-      <c r="L54" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10"/>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10"/>
-      <c r="AA54" s="10"/>
-      <c r="AB54" s="10"/>
-    </row>
-    <row r="55" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D55" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F55/25," Multiple-choice Quizzes |
+      <c r="L56" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+      <c r="Z56" s="10"/>
+      <c r="AA56" s="10"/>
+      <c r="AB56" s="10"/>
+    </row>
+    <row r="57" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F57/25," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H55, G55, F55),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A55), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L55, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+| Price | ₱",IF(H57, G57, F57),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A57), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L57, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
         <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
  - Ready na ang answer key at di ka na magsasagot ng questions. 
  - Masanay ang students sa pagsagot ng multiple choice test. 
- - Parallel ang quiz items sa questions na lalabas sa First Summative test. 
- ---
+ - Parallel ang quiz items sa questions na lalabas sa Summative test at Term Exam. 
+---
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content | 4 Multiple-choice Quizzes |
+| Content |4 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
 | Price | ₱100|
 ---
 📥 **I-fill out ang Order Form**
 {{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-mq" height="850" &gt;}}
----
-**Quiz 1.1: Undefined Terms and Basic Geometric Figures** (20 items)
-  - Lesson 1.01: Basic Geometric Figures and Notation
-**Quiz 1.2: Parallel and Perpendicular Lines** (30 items)
-  - Lesson 1.02: Parallel and Perpendicular Lines
-  - Lesson 1.03: Angle Relationships Formed by Parallel Lines and a Transversal
-  - Lesson 1.04: Finding Angle Measures Using Line and Angle Relationships
-**Quiz 1.3: Relations and Functions** (30 items)
-  - Lesson 1.05: Relations and Functions
-  - Lesson 1.06: Domain and Range of Functions
-  - Lesson 1.07: Representing Relationships as Functions
-  - Lesson 1.08.1: Slope and Zeros of Linear Functions from Graphs
-  - Lesson 1.08.2: Slope and Zeros of Linear Functions from Equations
-  - Lesson 1.08.3: Slope and Zeros of Linear Functions from Tables
-**Quiz 1.4: Graphing Linear Functions** (24 items)
-  - Lesson 1.09.1: Graphing Linear Functions and Identifying Domain
-  - Lesson 1.09.2: Graphing Linear Functions and Identifying Range
-  - Lesson 1.09.3: Graphing Linear Functions and Finding Intercepts
-  - Lesson 1.09.4: Graphing Linear Functions and Determining Slope
-  - Lesson 1.10: Linear Models in Real-Life Situations
-  - Lesson 1.11: Solving Problems Involving Linear Functions
 ---
 🛒 **Payment Methods**
 | Method | Account Details | Payment Amount |
@@ -8077,70 +8691,68 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
 </v>
       </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="9">
+      <c r="E57" s="4"/>
+      <c r="F57" s="9">
         <v>100</v>
       </c>
-      <c r="G55" s="9"/>
-      <c r="H55" s="4" t="b">
+      <c r="G57" s="9"/>
+      <c r="H57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I57" s="5">
         <v>46176</v>
       </c>
-      <c r="J55" s="4" t="b">
+      <c r="J57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K55" s="17">
+      <c r="K57" s="17">
         <v>46176</v>
       </c>
-      <c r="L55" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="10"/>
-      <c r="Y55" s="10"/>
-      <c r="Z55" s="10"/>
-      <c r="AA55" s="10"/>
-      <c r="AB55" s="10"/>
-    </row>
-    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D56" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F56/25," Multiple-choice Quizzes |
+      <c r="L57" s="4"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
+      <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
+      <c r="X57" s="10"/>
+      <c r="Y57" s="10"/>
+      <c r="Z57" s="10"/>
+      <c r="AA57" s="10"/>
+      <c r="AB57" s="10"/>
+    </row>
+    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F58/25," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H56, G56, F56),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A56), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L56, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+| Price | ₱",IF(H58, G58, F58),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A58), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L58, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
         <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
  - Ready na ang answer key at di ka na magsasagot ng questions. 
  - Masanay ang students sa pagsagot ng multiple choice test. 
- - Parallel ang quiz items sa questions na lalabas sa First Summative test. 
- ---
+ - Parallel ang quiz items sa questions na lalabas sa Summative test at Term Exam. 
+---
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content | 4 Multiple-choice Quizzes |
+| Content |4 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
 | Price | ₱100|
@@ -8202,58 +8814,58 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
 </v>
       </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="9">
+      <c r="E58" s="4"/>
+      <c r="F58" s="9">
         <v>100</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="4" t="b">
+      <c r="G58" s="9"/>
+      <c r="H58" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I58" s="5">
         <v>46176</v>
       </c>
-      <c r="J56" s="4" t="b">
+      <c r="J58" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K56" s="17">
+      <c r="K58" s="17">
         <v>46176</v>
       </c>
-      <c r="L56" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="10"/>
-      <c r="AA56" s="10"/>
-      <c r="AB56" s="10"/>
-    </row>
-    <row r="57" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-    </row>
-    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" s="8" t="str">
+      <c r="L58" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
+      <c r="V58" s="10"/>
+      <c r="W58" s="10"/>
+      <c r="X58" s="10"/>
+      <c r="Y58" s="10"/>
+      <c r="Z58" s="10"/>
+      <c r="AA58" s="10"/>
+      <c r="AB58" s="10"/>
+    </row>
+    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8297,7 +8909,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E58" s="4" t="str">
+      <c r="E60" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8342,53 +8954,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F58" s="9">
+      <c r="F60" s="9">
         <v>120</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G60" s="9">
         <v>84</v>
       </c>
-      <c r="H58" s="4" t="b">
+      <c r="H60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I60" s="5">
         <v>46176</v>
       </c>
-      <c r="J58" s="4" t="b">
+      <c r="J60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K58" s="17">
+      <c r="K60" s="17">
         <v>46176</v>
       </c>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="10"/>
-      <c r="S58" s="10"/>
-      <c r="T58" s="10"/>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-      <c r="Y58" s="10"/>
-      <c r="Z58" s="10"/>
-      <c r="AA58" s="10"/>
-      <c r="AB58" s="10"/>
-    </row>
-    <row r="59" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D59" s="8" t="str">
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
+      <c r="X60" s="10"/>
+      <c r="Y60" s="10"/>
+      <c r="Z60" s="10"/>
+      <c r="AA60" s="10"/>
+      <c r="AB60" s="10"/>
+    </row>
+    <row r="61" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -8434,7 +9046,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E59" s="4" t="str">
+      <c r="E61" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -8481,36 +9093,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F59" s="15">
+      <c r="F61" s="15">
         <v>165</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G61" s="15">
         <v>115</v>
       </c>
-      <c r="H59" s="4" t="b">
+      <c r="H61" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I61" s="5">
         <v>46176</v>
       </c>
-      <c r="J59" s="4" t="b">
+      <c r="J61" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K59" s="17">
+      <c r="K61" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D60" s="8" t="str">
+    <row r="62" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -8556,7 +9168,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E60" s="4" t="str">
+      <c r="E62" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -8603,36 +9215,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F60" s="15">
+      <c r="F62" s="15">
         <v>350</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G62" s="15">
         <v>245</v>
       </c>
-      <c r="H60" s="4" t="b">
+      <c r="H62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I62" s="5">
         <v>46176</v>
       </c>
-      <c r="J60" s="4" t="b">
+      <c r="J62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K60" s="17">
+      <c r="K62" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="8" t="str">
+    <row r="63" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8676,7 +9288,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E61" s="4" t="str">
+      <c r="E63" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8721,53 +9333,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F61" s="9">
+      <c r="F63" s="9">
         <v>120</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G63" s="9">
         <v>84</v>
       </c>
-      <c r="H61" s="4" t="b">
+      <c r="H63" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I63" s="5">
         <v>46176</v>
       </c>
-      <c r="J61" s="4" t="b">
+      <c r="J63" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K61" s="17">
+      <c r="K63" s="17">
         <v>46176</v>
       </c>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="10"/>
-      <c r="Z61" s="10"/>
-      <c r="AA61" s="10"/>
-      <c r="AB61" s="10"/>
-    </row>
-    <row r="62" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D62" s="8" t="str">
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="10"/>
+      <c r="Y63" s="10"/>
+      <c r="Z63" s="10"/>
+      <c r="AA63" s="10"/>
+      <c r="AB63" s="10"/>
+    </row>
+    <row r="64" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -8813,7 +9425,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E62" s="4" t="str">
+      <c r="E64" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -8860,36 +9472,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F62" s="15">
+      <c r="F64" s="15">
         <v>165</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G64" s="15">
         <v>115</v>
       </c>
-      <c r="H62" s="4" t="b">
+      <c r="H64" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I64" s="5">
         <v>46176</v>
       </c>
-      <c r="J62" s="4" t="b">
+      <c r="J64" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K62" s="17">
+      <c r="K64" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D63" s="8" t="str">
+    <row r="65" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -8935,7 +9547,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E63" s="4" t="str">
+      <c r="E65" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -8982,36 +9594,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F63" s="15">
+      <c r="F65" s="15">
         <v>350</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G65" s="15">
         <v>245</v>
       </c>
-      <c r="H63" s="4" t="b">
+      <c r="H65" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I65" s="5">
         <v>46176</v>
       </c>
-      <c r="J63" s="4" t="b">
+      <c r="J65" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K63" s="17">
+      <c r="K65" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D64" s="8" t="str">
+    <row r="66" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D66" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9055,7 +9667,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E64" s="4" t="str">
+      <c r="E66" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9100,53 +9712,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F64" s="9">
+      <c r="F66" s="9">
         <v>120</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G66" s="9">
         <v>84</v>
       </c>
-      <c r="H64" s="4" t="b">
+      <c r="H66" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I66" s="5">
         <v>46176</v>
       </c>
-      <c r="J64" s="4" t="b">
+      <c r="J66" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K64" s="17">
+      <c r="K66" s="17">
         <v>46176</v>
       </c>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="10"/>
-      <c r="T64" s="10"/>
-      <c r="U64" s="10"/>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="10"/>
-      <c r="Z64" s="10"/>
-      <c r="AA64" s="10"/>
-      <c r="AB64" s="10"/>
-    </row>
-    <row r="65" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D65" s="8" t="str">
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+      <c r="Z66" s="10"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="10"/>
+    </row>
+    <row r="67" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9192,7 +9804,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E65" s="4" t="str">
+      <c r="E67" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9239,36 +9851,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F65" s="15">
+      <c r="F67" s="15">
         <v>165</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G67" s="15">
         <v>115</v>
       </c>
-      <c r="H65" s="4" t="b">
+      <c r="H67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I67" s="5">
         <v>46176</v>
       </c>
-      <c r="J65" s="4" t="b">
+      <c r="J67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K65" s="17">
+      <c r="K67" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D66" s="8" t="str">
+    <row r="68" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D68" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9314,7 +9926,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E66" s="4" t="str">
+      <c r="E68" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9361,36 +9973,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F66" s="15">
+      <c r="F68" s="15">
         <v>350</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G68" s="15">
         <v>245</v>
       </c>
-      <c r="H66" s="4" t="b">
+      <c r="H68" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I68" s="5">
         <v>46176</v>
       </c>
-      <c r="J66" s="4" t="b">
+      <c r="J68" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K66" s="17">
+      <c r="K68" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="8" t="str">
+    <row r="69" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D69" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9434,7 +10046,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E67" s="4" t="str">
+      <c r="E69" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9479,53 +10091,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F67" s="9">
+      <c r="F69" s="9">
         <v>120</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G69" s="9">
         <v>84</v>
       </c>
-      <c r="H67" s="4" t="b">
+      <c r="H69" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I69" s="5">
         <v>46176</v>
       </c>
-      <c r="J67" s="4" t="b">
+      <c r="J69" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K67" s="17">
+      <c r="K69" s="17">
         <v>46176</v>
       </c>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
-      <c r="V67" s="10"/>
-      <c r="W67" s="10"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="10"/>
-      <c r="Z67" s="10"/>
-      <c r="AA67" s="10"/>
-      <c r="AB67" s="10"/>
-    </row>
-    <row r="68" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="8" t="str">
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="10"/>
+      <c r="Z69" s="10"/>
+      <c r="AA69" s="10"/>
+      <c r="AB69" s="10"/>
+    </row>
+    <row r="70" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9571,7 +10183,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E68" s="4" t="str">
+      <c r="E70" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9618,36 +10230,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F68" s="15">
+      <c r="F70" s="15">
         <v>165</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G70" s="15">
         <v>115</v>
       </c>
-      <c r="H68" s="4" t="b">
+      <c r="H70" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I70" s="5">
         <v>46176</v>
       </c>
-      <c r="J68" s="4" t="b">
+      <c r="J70" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K68" s="17">
+      <c r="K70" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D69" s="8" t="str">
+    <row r="71" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9693,7 +10305,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E69" s="4" t="str">
+      <c r="E71" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9740,36 +10352,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F69" s="15">
+      <c r="F71" s="15">
         <v>350</v>
       </c>
-      <c r="G69" s="15">
+      <c r="G71" s="15">
         <v>245</v>
       </c>
-      <c r="H69" s="4" t="b">
+      <c r="H71" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I71" s="5">
         <v>46176</v>
       </c>
-      <c r="J69" s="4" t="b">
+      <c r="J71" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K69" s="17">
+      <c r="K71" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" s="8" t="str">
+    <row r="72" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9813,7 +10425,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E70" s="4" t="str">
+      <c r="E72" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9858,53 +10470,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F70" s="9">
+      <c r="F72" s="9">
         <v>120</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G72" s="9">
         <v>84</v>
       </c>
-      <c r="H70" s="4" t="b">
+      <c r="H72" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I72" s="5">
         <v>46176</v>
       </c>
-      <c r="J70" s="4" t="b">
+      <c r="J72" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K70" s="17">
+      <c r="K72" s="17">
         <v>46176</v>
       </c>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
-      <c r="R70" s="10"/>
-      <c r="S70" s="10"/>
-      <c r="T70" s="10"/>
-      <c r="U70" s="10"/>
-      <c r="V70" s="10"/>
-      <c r="W70" s="10"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="10"/>
-      <c r="Z70" s="10"/>
-      <c r="AA70" s="10"/>
-      <c r="AB70" s="10"/>
-    </row>
-    <row r="71" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D71" s="8" t="str">
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
+      <c r="X72" s="10"/>
+      <c r="Y72" s="10"/>
+      <c r="Z72" s="10"/>
+      <c r="AA72" s="10"/>
+      <c r="AB72" s="10"/>
+    </row>
+    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9950,7 +10562,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E71" s="4" t="str">
+      <c r="E73" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9997,36 +10609,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F71" s="15">
+      <c r="F73" s="15">
         <v>165</v>
       </c>
-      <c r="G71" s="15">
+      <c r="G73" s="15">
         <v>115</v>
       </c>
-      <c r="H71" s="4" t="b">
+      <c r="H73" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I73" s="5">
         <v>46176</v>
       </c>
-      <c r="J71" s="4" t="b">
+      <c r="J73" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K71" s="17">
+      <c r="K73" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" s="8" t="str">
+    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10072,7 +10684,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E72" s="4" t="str">
+      <c r="E74" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10119,36 +10731,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F72" s="15">
+      <c r="F74" s="15">
         <v>350</v>
       </c>
-      <c r="G72" s="15">
+      <c r="G74" s="15">
         <v>245</v>
       </c>
-      <c r="H72" s="4" t="b">
+      <c r="H74" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I74" s="5">
         <v>46176</v>
       </c>
-      <c r="J72" s="4" t="b">
+      <c r="J74" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K72" s="17">
+      <c r="K74" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="D73" s="8" t="str">
+    <row r="75" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10192,7 +10804,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E73" s="4" t="str">
+      <c r="E75" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10237,53 +10849,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F73" s="9">
+      <c r="F75" s="9">
         <v>120</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G75" s="9">
         <v>84</v>
       </c>
-      <c r="H73" s="4" t="b">
+      <c r="H75" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I75" s="5">
         <v>46176</v>
       </c>
-      <c r="J73" s="4" t="b">
+      <c r="J75" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K73" s="17">
+      <c r="K75" s="17">
         <v>46176</v>
       </c>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
-      <c r="V73" s="10"/>
-      <c r="W73" s="10"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="10"/>
-      <c r="Z73" s="10"/>
-      <c r="AA73" s="10"/>
-      <c r="AB73" s="10"/>
-    </row>
-    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D74" s="8" t="str">
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="10"/>
+      <c r="X75" s="10"/>
+      <c r="Y75" s="10"/>
+      <c r="Z75" s="10"/>
+      <c r="AA75" s="10"/>
+      <c r="AB75" s="10"/>
+    </row>
+    <row r="76" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10329,7 +10941,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E74" s="4" t="str">
+      <c r="E76" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10376,36 +10988,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F74" s="15">
+      <c r="F76" s="15">
         <v>165</v>
       </c>
-      <c r="G74" s="15">
+      <c r="G76" s="15">
         <v>115</v>
       </c>
-      <c r="H74" s="4" t="b">
+      <c r="H76" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I76" s="5">
         <v>46176</v>
       </c>
-      <c r="J74" s="4" t="b">
+      <c r="J76" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K74" s="17">
+      <c r="K76" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="8" t="str">
+    <row r="77" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D77" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10451,7 +11063,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E75" s="4" t="str">
+      <c r="E77" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10498,36 +11110,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F75" s="15">
+      <c r="F77" s="15">
         <v>350</v>
       </c>
-      <c r="G75" s="15">
+      <c r="G77" s="15">
         <v>245</v>
       </c>
-      <c r="H75" s="4" t="b">
+      <c r="H77" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I77" s="5">
         <v>46176</v>
       </c>
-      <c r="J75" s="4" t="b">
+      <c r="J77" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K75" s="17">
+      <c r="K77" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D76" s="8" t="str">
+    <row r="78" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D78" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10571,7 +11183,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E76" s="4" t="str">
+      <c r="E78" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10616,53 +11228,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F76" s="9">
+      <c r="F78" s="9">
         <v>120</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G78" s="9">
         <v>84</v>
       </c>
-      <c r="H76" s="4" t="b">
+      <c r="H78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I76" s="5">
+      <c r="I78" s="5">
         <v>46176</v>
       </c>
-      <c r="J76" s="4" t="b">
+      <c r="J78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K76" s="17">
+      <c r="K78" s="17">
         <v>46176</v>
       </c>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
-      <c r="N76" s="10"/>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-      <c r="Q76" s="10"/>
-      <c r="R76" s="10"/>
-      <c r="S76" s="10"/>
-      <c r="T76" s="10"/>
-      <c r="U76" s="10"/>
-      <c r="V76" s="10"/>
-      <c r="W76" s="10"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="10"/>
-      <c r="Z76" s="10"/>
-      <c r="AA76" s="10"/>
-      <c r="AB76" s="10"/>
-    </row>
-    <row r="77" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="8" t="str">
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="10"/>
+      <c r="U78" s="10"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="10"/>
+      <c r="X78" s="10"/>
+      <c r="Y78" s="10"/>
+      <c r="Z78" s="10"/>
+      <c r="AA78" s="10"/>
+      <c r="AB78" s="10"/>
+    </row>
+    <row r="79" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10708,7 +11320,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E77" s="4" t="str">
+      <c r="E79" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10755,36 +11367,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F77" s="15">
+      <c r="F79" s="15">
         <v>165</v>
       </c>
-      <c r="G77" s="15">
+      <c r="G79" s="15">
         <v>115</v>
       </c>
-      <c r="H77" s="4" t="b">
+      <c r="H79" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I77" s="5">
+      <c r="I79" s="5">
         <v>46176</v>
       </c>
-      <c r="J77" s="4" t="b">
+      <c r="J79" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K77" s="17">
+      <c r="K79" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B78" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D78" s="8" t="str">
+    <row r="80" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D80" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10830,7 +11442,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E78" s="4" t="str">
+      <c r="E80" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10877,36 +11489,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F78" s="15">
+      <c r="F80" s="15">
         <v>350</v>
       </c>
-      <c r="G78" s="15">
+      <c r="G80" s="15">
         <v>245</v>
       </c>
-      <c r="H78" s="4" t="b">
+      <c r="H80" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I78" s="5">
+      <c r="I80" s="5">
         <v>46176</v>
       </c>
-      <c r="J78" s="4" t="b">
+      <c r="J80" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K78" s="17">
+      <c r="K80" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D79" s="8" t="str">
+    <row r="81" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10950,7 +11562,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E79" s="4" t="str">
+      <c r="E81" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10995,53 +11607,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F79" s="9">
+      <c r="F81" s="9">
         <v>120</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G81" s="9">
         <v>84</v>
       </c>
-      <c r="H79" s="4" t="b">
+      <c r="H81" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I79" s="5">
+      <c r="I81" s="5">
         <v>46176</v>
       </c>
-      <c r="J79" s="4" t="b">
+      <c r="J81" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K79" s="17">
+      <c r="K81" s="17">
         <v>46176</v>
       </c>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
-      <c r="V79" s="10"/>
-      <c r="W79" s="10"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="10"/>
-      <c r="Z79" s="10"/>
-      <c r="AA79" s="10"/>
-      <c r="AB79" s="10"/>
-    </row>
-    <row r="80" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D80" s="8" t="str">
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="10"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
+      <c r="V81" s="10"/>
+      <c r="W81" s="10"/>
+      <c r="X81" s="10"/>
+      <c r="Y81" s="10"/>
+      <c r="Z81" s="10"/>
+      <c r="AA81" s="10"/>
+      <c r="AB81" s="10"/>
+    </row>
+    <row r="82" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11087,7 +11699,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E80" s="4" t="str">
+      <c r="E82" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11134,36 +11746,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F80" s="15">
+      <c r="F82" s="15">
         <v>165</v>
       </c>
-      <c r="G80" s="15">
+      <c r="G82" s="15">
         <v>115</v>
       </c>
-      <c r="H80" s="4" t="b">
+      <c r="H82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I80" s="5">
+      <c r="I82" s="5">
         <v>46176</v>
       </c>
-      <c r="J80" s="4" t="b">
+      <c r="J82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K80" s="17">
+      <c r="K82" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D81" s="8" t="str">
+    <row r="83" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11209,7 +11821,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E81" s="4" t="str">
+      <c r="E83" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11256,82 +11868,74 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F81" s="15">
+      <c r="F83" s="15">
         <v>350</v>
       </c>
-      <c r="G81" s="15">
+      <c r="G83" s="15">
         <v>245</v>
       </c>
-      <c r="H81" s="4" t="b">
+      <c r="H83" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I81" s="5">
+      <c r="I83" s="5">
         <v>46176</v>
       </c>
-      <c r="J81" s="4" t="b">
+      <c r="J83" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K81" s="17">
+      <c r="K83" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-    </row>
-    <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-    </row>
-    <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F84" s="19"/>
       <c r="G84" s="19"/>
     </row>
-    <row r="85" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F85" s="19"/>
       <c r="G85" s="19"/>
     </row>
-    <row r="86" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F86" s="19"/>
       <c r="G86" s="19"/>
     </row>
-    <row r="87" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F87" s="19"/>
       <c r="G87" s="19"/>
     </row>
-    <row r="88" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F88" s="19"/>
       <c r="G88" s="19"/>
     </row>
-    <row r="89" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F89" s="19"/>
       <c r="G89" s="19"/>
     </row>
-    <row r="90" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F90" s="19"/>
       <c r="G90" s="19"/>
     </row>
-    <row r="91" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F91" s="19"/>
       <c r="G91" s="19"/>
     </row>
-    <row r="92" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F92" s="19"/>
       <c r="G92" s="19"/>
     </row>
-    <row r="93" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F93" s="19"/>
       <c r="G93" s="19"/>
     </row>
-    <row r="94" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F94" s="19"/>
       <c r="G94" s="19"/>
     </row>
-    <row r="95" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F95" s="19"/>
       <c r="G95" s="19"/>
     </row>
-    <row r="96" spans="1:11" ht="12.75" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F96" s="19"/>
       <c r="G96" s="19"/>
     </row>
@@ -14878,6 +15482,14 @@
     <row r="982" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F982" s="19"/>
       <c r="G982" s="19"/>
+    </row>
+    <row r="983" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F983" s="19"/>
+      <c r="G983" s="19"/>
+    </row>
+    <row r="984" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F984" s="19"/>
+      <c r="G984" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14906,51 +15518,53 @@
     <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="C26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
     <hyperlink ref="C27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C36" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C37" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C38" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C39" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C40" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C41" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C42" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C43" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C47" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C48" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C49" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C50" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C51" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C52" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C53" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C54" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C55" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C56" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C58" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C59" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C60" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C61" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C62" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C63" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C64" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C65" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C66" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C67" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C68" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C70" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C71" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C72" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C73" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C74" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C75" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C76" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C77" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C78" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C79" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C80" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C81" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C35" r:id="rId70" xr:uid="{D2F92652-BCD8-9046-8224-7D862D4D72B8}"/>
+    <hyperlink ref="C31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C32" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C39" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C41" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C42" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C43" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C44" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C45" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C49" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C50" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C51" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C52" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C53" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C54" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C55" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C56" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C57" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C58" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C60" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C61" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C62" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C63" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C64" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C65" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C67" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C69" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C70" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C71" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C72" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C73" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C74" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C75" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C76" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C77" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C78" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C79" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C80" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C81" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C82" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C83" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C30" r:id="rId70" xr:uid="{C3D8895E-36F9-C446-9032-98D1DBA560B2}"/>
+    <hyperlink ref="C36" r:id="rId71" xr:uid="{01D04C71-5B69-CD49-B99C-9F3396BA5C94}"/>
+    <hyperlink ref="C37" r:id="rId72" xr:uid="{993E0396-71F4-7543-B9D1-2323DD4B1A4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14961,92 +15575,97 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.15">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>205</v>
+        <v>165</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="24" t="str">
+        <f>CONCATENATE("
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).")</f>
+        <v xml:space="preserve">
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>1</v>
@@ -15063,19 +15682,19 @@
     </row>
     <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="F10" s="1" t="b">
         <v>1</v>
@@ -15099,19 +15718,19 @@
     </row>
     <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
@@ -15135,19 +15754,19 @@
     </row>
     <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="F12" s="1" t="b">
         <v>0</v>
@@ -15171,19 +15790,19 @@
     </row>
     <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
@@ -15207,42 +15826,216 @@
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>232</v>
+        <v>156</v>
+      </c>
+      <c r="D17" s="10" t="str">
+        <f>CONCATENATE(_xlfn._LONGTEXT("- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo. "," 
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Table of Specifications (21st Century format)  
+- Number of days: "), Sheet1!Q29," days  
+- ", Sheet1!R29,_xlfn._LONGTEXT("-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadube","mrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*"))</f>
+        <v>- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Table of Specifications (21st Century format)  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>197</v>
+        <v>158</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="10"/>
+      <c r="F18" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="27"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>244</v>
+      </c>
+      <c r="B30" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>245</v>
+      </c>
+      <c r="B31" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>246</v>
+      </c>
+      <c r="B32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>252</v>
+      </c>
+      <c r="B37" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>257</v>
+      </c>
+      <c r="B44" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
+        <v>258</v>
+      </c>
+      <c r="B45" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="273">
   <si>
     <t>ProductID</t>
   </si>

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="272">
   <si>
     <t>ProductID</t>
   </si>

--- a/HugoBlog.xlsx
+++ b/HugoBlog.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="280">
   <si>
     <t>ProductID</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Grade 7 T3 First Summative Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G7-T3-S1-PP</t>
-  </si>
-  <si>
     <t>Grade 7 T3 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>Grade 8 T3 First Summative Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G8-T3-S1-PP</t>
-  </si>
-  <si>
     <t>Grade 8 T3 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>Grade 9 T3 First Summative Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G9-T3-S1-PP</t>
-  </si>
-  <si>
     <t>Grade 9 T3 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Grade 10 T3 First Summative Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G10-T3-S1-PP</t>
-  </si>
-  <si>
     <t>Grade 10 T3 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
@@ -231,24 +219,9 @@
     <t>G7-T1-S1-BP</t>
   </si>
   <si>
-    <t>Grade 7 T1 First Summative Test + TOS + Answer Key (Basic)</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771580685/s2on3kech3iylmxfxawn.jpg</t>
-  </si>
-  <si>
     <t>G7-T1-S1-SP</t>
   </si>
   <si>
-    <t>Grade 7 T1 First Summative Test + TOS + Answer Key (Standard)</t>
-  </si>
-  <si>
-    <t>G7-T1-S1-PP</t>
-  </si>
-  <si>
-    <t>Grade 7 T1 First Summative Test + TOS + Answer Key (Premium)</t>
-  </si>
-  <si>
     <t>G8-T1-S1-BP</t>
   </si>
   <si>
@@ -264,33 +237,15 @@
     <t>Grade 8 T1 First Summative Test + TOS + Answer Key (Standard)</t>
   </si>
   <si>
-    <t>G8-T1-S1-PP</t>
-  </si>
-  <si>
     <t>Grade 8 T1 First Summative Test + TOS + Answer Key (Premium)</t>
   </si>
   <si>
     <t>G9-T1-S1-BP</t>
   </si>
   <si>
-    <t>Grade 9 T1 First Summative Test + TOS + Answer Key (Basic)</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1771581041/bwg96ufbzxt2qcdwzb1d.jpg</t>
-  </si>
-  <si>
     <t>G9-T1-S1-SP</t>
   </si>
   <si>
-    <t>Grade 9 T1 First Summative Test + TOS + Answer Key (Standard)</t>
-  </si>
-  <si>
-    <t>G9-T1-S1-PP</t>
-  </si>
-  <si>
-    <t>Grade 9 T1 First Summative Test + TOS + Answer Key (Premium)</t>
-  </si>
-  <si>
     <t>G10-T1-S1-BP</t>
   </si>
   <si>
@@ -304,9 +259,6 @@
   </si>
   <si>
     <t>Grade 10 T1 First Summative Test + TOS + Answer Key (Standard)</t>
-  </si>
-  <si>
-    <t>G10-T1-S1-PP</t>
   </si>
   <si>
     <t>Grade 10 T1 First Summative Test + TOS + Answer Key (Premium)</t>
@@ -418,9 +370,6 @@
   </si>
   <si>
     <t>Grade 9 T1 Multiple-Choice Quizzes + Answer Keys</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1770982592/npoqdwippiz4cxvg9bii.jpg</t>
   </si>
   <si>
     <t>G10-T1-MQ</t>
@@ -884,23 +833,6 @@
 | Content | </t>
   </si>
   <si>
-    <t xml:space="preserve">---
-🛒 **Payment Methods**
-| Method | Account Details | Payment Amount |
-|---|---|---|
-| 💳 ATM (Landbank) | 0695077289 | Exact Amount |
-| 💸 GCash | 09128389571 | Add ₱15 convenience fee |
-| 💸 Maya | 09128389571 | Add ₱15 convenience fee |
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
-</t>
-  </si>
-  <si>
     <t>Grade 7</t>
   </si>
   <si>
@@ -1042,9 +974,6 @@
     <t>G7-T1-S2-BP</t>
   </si>
   <si>
-    <t>Grade 7 T1 Second Summative Test + TOS + Answer Key (Basic)</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784692768/blzn2f4qf4csagllrdmj.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784692772/mlwmihwoocbpcd5of6rx.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784692776/adpmufdqkz5qxw5yzj0p.png</t>
   </si>
   <si>
@@ -1081,99 +1010,66 @@
     <t>G7-T3-TE-SP</t>
   </si>
   <si>
-    <t>G7-T3-TE-PP</t>
-  </si>
-  <si>
     <t>G8-T3-TE-BP</t>
   </si>
   <si>
     <t>G8-T3-TE-SP</t>
   </si>
   <si>
-    <t>G8-T3-TE-PP</t>
-  </si>
-  <si>
     <t>G9-T3-TE-BP</t>
   </si>
   <si>
     <t>G9-T3-TE-SP</t>
   </si>
   <si>
-    <t>G9-T3-TE-PP</t>
-  </si>
-  <si>
     <t>G10-T3-TE-BP</t>
   </si>
   <si>
     <t>G10-T3-TE-SP</t>
   </si>
   <si>
-    <t>G10-T3-TE-PP</t>
-  </si>
-  <si>
     <t>G7-T1-TE-BP</t>
   </si>
   <si>
     <t>G7-T1-TE-SP</t>
   </si>
   <si>
-    <t>G7-T1-TE-PP</t>
-  </si>
-  <si>
     <t>G8-T1-TE-BP</t>
   </si>
   <si>
     <t>G8-T1-TE-SP</t>
   </si>
   <si>
-    <t>G8-T1-TE-PP</t>
-  </si>
-  <si>
     <t>G9-T1-TE-BP</t>
   </si>
   <si>
     <t>G9-T1-TE-SP</t>
   </si>
   <si>
-    <t>G9-T1-TE-PP</t>
-  </si>
-  <si>
     <t>G10-T1-TE-BP</t>
   </si>
   <si>
     <t>G10-T1-TE-SP</t>
   </si>
   <si>
-    <t>G10-T1-TE-PP</t>
-  </si>
-  <si>
     <t>G8-T2-TE-BP</t>
   </si>
   <si>
     <t>G8-T2-TE-SP</t>
   </si>
   <si>
-    <t>G8-T2-TE-PP</t>
-  </si>
-  <si>
     <t>G9-T2-TE-BP</t>
   </si>
   <si>
     <t>G9-T2-TE-SP</t>
   </si>
   <si>
-    <t>G9-T2-TE-PP</t>
-  </si>
-  <si>
     <t>G10-T2-TE-BP</t>
   </si>
   <si>
     <t>G10-T2-TE-SP</t>
   </si>
   <si>
-    <t>G10-T2-TE-PP</t>
-  </si>
-  <si>
     <t>TE</t>
   </si>
   <si>
@@ -1225,31 +1121,19 @@
     <t>SP</t>
   </si>
   <si>
-    <t>PP</t>
-  </si>
-  <si>
     <t>Basic Assessment Package</t>
   </si>
   <si>
     <t>Standard Assessment Package</t>
   </si>
   <si>
-    <t>Premium Assessment Package</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
     <t>Items</t>
   </si>
   <si>
-    <t>ST Regular Basic</t>
-  </si>
-  <si>
     <t>G9-T1-S2-BP</t>
-  </si>
-  <si>
-    <t>Grade 9 T1 Second Summative Test + TOS + Answer Key (Basic)</t>
   </si>
   <si>
     <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784731784/ptqhzxe6hdaphiivprrc.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784731787/jc6dwnedukuiwimgdgxv.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784731789/aidqozqvzsxtxmtppi1c.png</t>
@@ -1296,6 +1180,181 @@
 - Represent linear relationships found in real-life situations using different representations.
 - Solve problems involving linear functions.
 - Determine conditions that guarantee parallelism and perpendicularity of lines.</t>
+  </si>
+  <si>
+    <t>Pieces</t>
+  </si>
+  <si>
+    <t>- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/).</t>
+  </si>
+  <si>
+    <t>---
+📑 **Topics Covered**
+**Quiz 1.01.1: Basic Undefined Terms and Geometric Notation** (35 items)
+  - Lesson 1. 1.01.1: Basic Undefined Terms and Geometric Notation
+  - Lesson 1. 1.01.2: Constructing Parallel and Perpendicular Lines
+**Quiz 1.02.1: Angles Formed by Parallel Lines and a Transversal** (30 items)
+  - Lesson 1. 1.02.1: Angles Formed by Parallel Lines and a Transversal
+  - Lesson 1. 1.02.2: Solving Angle Measures with Parallel and Perpendicular Lines
+**Quiz 1.03.1: Introduction to Relations and Functions** (30 items)
+  - Lesson 1. 1.03.1: Introduction to Relations and Functions
+  - Lesson 1. 1.03.2: Domain of a Function
+  - Lesson 1. 1.03.3: Range of a Function
+**Quiz 1.04.1: Representing Relationships as Functions** (30 items)
+  - Lesson 1. 1.04.1: Representing Relationships as Functions
+  - Lesson 1. 1.04.2: Slope of Linear Functions from Graphs
+  - Lesson 1. 1.04.3: Zeros of Linear Functions from Graphs
+  - Lesson 1. 1.04.4: Slope of Linear Functions from Equations
+  - Lesson 1. 1.04.5: Zeros of Linear Functions from Equations
+  - Lesson 1. 1.04.6: Slope of Linear Functions from Tables
+  - Lesson 1. 1.04.7: Zeros of Linear Functions from Tables
+**Quiz 1.05.1: Graphing Linear Functions: Domain and Range** (35 items)
+  - Lesson 1. 1.05.1: Graphing Linear Functions: Domain and Range
+  - Lesson 1. 1.05.2: Graphing Linear Function - Intercepts and Slope
+  - Lesson 1. 1.05.3: Representing Real-Life Linear Relationships
+**Quiz 1.06.1: Solving Problems Involving Linear Functions** (30 items)
+  - Lesson 1. 1.06.1: Solving Problems Involving Linear Functions
+  - Lesson 1. 1.06.2: Conditions that Guarantee Parallelism
+  - Lesson 1. 1.06.3: Conditions that Guarantee Perpendicularity
+**Quiz 1.07.1: Classifying Quadrilaterals** (35 items)
+  - Lesson 1. 1.07.1: Classifying Quadrilaterals
+  - Lesson 1. 1.07.2: Properties of Parallelograms
+**Quiz 1.08.1: Finding Lengths in Parallelograms** (30 items)
+  - Lesson 1. 1.08.1: Finding Side Lengths in Parallelograms
+  - Lesson 1. 1.08.2: Finding Angle Measures in Parallelograms
+  - Lesson 1. 1.08.3: Finding Perpendicular Heights in Parallelograms
+  - Lesson 1. 1.08.4: Finding Diagonal Measures in Parallelograms
+**Quiz 1.09.1: Problem Solving with Parallelograms** (30 items)
+  - Lesson 1. 1.09.1: Problem Solving with Parallelograms and Rectangles
+  - Lesson 1. 1.09.2: Problem Solving with Squares and Rhombuses
+**Quiz 1.10.1: Proving Properties of Parallelograms** (25 items)
+  - Lesson 1. 1.10.1: Proving Properties of Parallelograms</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dadubemrv/image/upload/v1784868820/ozzzxppeyyvj0s2tjymk.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784868830/kgezh16t4knvga2qdead.png,https://res.cloudinary.com/dadubemrv/image/upload/v1784868834/juzddujgsxbdnu454ck5.png</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 First Summative Test + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 Second Summative Test + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 First Summative Test + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 Second Summative Test + Answer Key (Basic)</t>
+  </si>
+  <si>
+    <t>G7-T1-S2-SP</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 Second Summative Test + Answer Key + TOS (Standard)</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 First Summative Test + Answer Key + TOS (Standard)</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 First Summative Test + Answer Key + TOS (Standard)</t>
+  </si>
+  <si>
+    <t>G9-T1-S2-SP</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 Second Summative Test + Answer Key + TOS (Standard)</t>
+  </si>
+  <si>
+    <t>G7-T1-S1-CP</t>
+  </si>
+  <si>
+    <t>G8-T1-S1-CP</t>
+  </si>
+  <si>
+    <t>G9-T1-S1-CP</t>
+  </si>
+  <si>
+    <t>G10-T1-S1-CP</t>
+  </si>
+  <si>
+    <t>G7-T1-TE-CP</t>
+  </si>
+  <si>
+    <t>G8-T1-TE-CP</t>
+  </si>
+  <si>
+    <t>G9-T1-TE-CP</t>
+  </si>
+  <si>
+    <t>G10-T1-TE-CP</t>
+  </si>
+  <si>
+    <t>G8-T2-TE-CP</t>
+  </si>
+  <si>
+    <t>G9-T2-TE-CP</t>
+  </si>
+  <si>
+    <t>G10-T2-TE-CP</t>
+  </si>
+  <si>
+    <t>G7-T3-S1-CP</t>
+  </si>
+  <si>
+    <t>G8-T3-S1-CP</t>
+  </si>
+  <si>
+    <t>G9-T3-S1-CP</t>
+  </si>
+  <si>
+    <t>G10-T3-S1-CP</t>
+  </si>
+  <si>
+    <t>G7-T3-TE-CP</t>
+  </si>
+  <si>
+    <t>G8-T3-TE-CP</t>
+  </si>
+  <si>
+    <t>G9-T3-TE-CP</t>
+  </si>
+  <si>
+    <t>G10-T3-TE-CP</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 First Summative Test + Answer Key + TOS (Custom)</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Custom Assessment Package</t>
+  </si>
+  <si>
+    <t>25-50</t>
+  </si>
+  <si>
+    <t>G7-T1-S2-CP</t>
+  </si>
+  <si>
+    <t>Grade 7 T1 Second Summative Test + Answer Key + TOS (Custom)</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 First Summative Test + Answer Key + TOS (Custom)</t>
+  </si>
+  <si>
+    <t>G9-T1-S2-CP</t>
+  </si>
+  <si>
+    <t>Grade 9 T1 Second Summative Test + Answer Key + TOS (Custom)</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1711,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB984"/>
+  <dimension ref="A1:AB988"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
@@ -1690,25 +1749,28 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="N1" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="O1" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="P1" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="Q1" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="R1" t="s">
-        <v>263</v>
+        <v>231</v>
+      </c>
+      <c r="S1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1740,7 +1802,7 @@
 [Jonathan Bacolod](https://texmathpro.github.io/about/)  
 Owner and CEO  
 [TeXMathPro](https://texmathpro.github.io/): Math Teaching Beautified  
-[texmathpro@gmail.com](mailto:texmathpro@gmail.com?subj"&amp;"ect=Subscribe&amp;body=SUBSCRIBE)")</f>
+[texmathpro@gmail.com](mailto:texmathpro@gmail.com?subj"&amp;"ect=Subscribe&amp;body=SUBSCRIBE)", "{{&lt; adsense &gt;}}")</f>
         <v>Nabibigatan ka ba sa laptop at projector para sa PowerPoint presentations mo, KasaMath?  
 Tinatamad ka ba, walang time, o nahihirapang gumawa ng PowerPoint?
 I-download mo na itong ating **FREE printable Math handouts** para:
@@ -1761,7 +1823,7 @@
 [Jonathan Bacolod](https://texmathpro.github.io/about/)  
 Owner and CEO  
 [TeXMathPro](https://texmathpro.github.io/): Math Teaching Beautified  
-[texmathpro@gmail.com](mailto:texmathpro@gmail.com?subject=Subscribe&amp;body=SUBSCRIBE)</v>
+[texmathpro@gmail.com](mailto:texmathpro@gmail.com?subject=Subscribe&amp;body=SUBSCRIBE){{&lt; adsense &gt;}}</v>
       </c>
       <c r="F2" s="2">
         <v>500</v>
@@ -2071,10 +2133,10 @@
     </row>
     <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>16</v>
@@ -2193,13 +2255,13 @@
     </row>
     <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="D7" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -2328,13 +2390,13 @@
     </row>
     <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -2450,13 +2512,13 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -2572,13 +2634,13 @@
     </row>
     <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>30</v>
       </c>
       <c r="D10" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -2707,13 +2769,13 @@
     </row>
     <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -2829,13 +2891,13 @@
     </row>
     <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>265</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -2951,13 +3013,13 @@
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D13" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -3086,13 +3148,13 @@
     </row>
     <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -3208,13 +3270,13 @@
     </row>
     <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>266</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D15" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -3330,13 +3392,13 @@
     </row>
     <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D16" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -3465,13 +3527,13 @@
     </row>
     <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D17" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -3587,13 +3649,13 @@
     </row>
     <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D18" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -3709,13 +3771,13 @@
     </row>
     <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D19" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -3844,13 +3906,13 @@
     </row>
     <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D20" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -3966,13 +4028,13 @@
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -4088,13 +4150,13 @@
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D22" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -4223,13 +4285,13 @@
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D23" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -4345,13 +4407,13 @@
     </row>
     <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D24" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -4467,13 +4529,13 @@
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D25" s="8" t="str">
         <f>Sheet2!$D$2</f>
@@ -4602,13 +4664,13 @@
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D26" s="8" t="str">
         <f>Sheet2!$E$2</f>
@@ -4724,13 +4786,13 @@
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D27" s="8" t="str">
         <f>Sheet2!$F$2</f>
@@ -4850,36 +4912,31 @@
     </row>
     <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="D29" s="8" t="str">
         <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M29, " mo, ",Sheet1!O29," KasaMath? Kuha ka na ng ", Sheet1!P29,"!*
 **Bakit perfect para sa’yo ang ", Sheet1!P29,"?**
-",Sheet2!D$17, L29, _xlfn._LONGTEXT("
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
+",Sheet2!D$17, Sheet1!Q29," days  
+- ", Sheet1!R29,"-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS", L29, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A29), """ height=""850"" &gt;}}","
 ## Step 2: Payment and Delivery
 ### Payment Methods
-M","ag-send ka lang ng ₱"),Sheet1!F29," para sa **", Sheet1!M29,_xlfn._LONGTEXT("**. 
+Mag-send ka lang ng ₱",Sheet1!F29," para sa **", Sheet1!M29,_xlfn._LONGTEXT("**. 
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
@@ -4889,22 +4946,16 @@
   - Dimensions: A4 bond paper
   - Format: PDF, created using LaTeX
 - **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format", Sheet2!$D$6)</f>
+  - Format: PDF, created using LaTeX", Sheet2!$D$6)</f>
         <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 7 KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
 - Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
 - Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
 - Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
 - Number of days: 15 days  
 - 25-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS
 ---
 📑 **Competencies Covered**
 - Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
@@ -4914,22 +4965,15 @@
 - Classify polygons whether they are convex or non-convex.
 - Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
 ---
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s1-bp" height="850" &gt;}}
 ## Step 2: Payment and Delivery
 ### Payment Methods
-Mag-send ka lang ng ₱60 para sa **First Summative test**. 
+Mag-send ka lang ng ₱59 para sa **First Summative test**. 
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+**Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
@@ -4941,17 +4985,775 @@
   - Format: PDF, created using LaTeX
 - **Answer Key**
   - Format: PDF, created using LaTeX
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="9">
+        <v>59</v>
+      </c>
+      <c r="G29" s="9">
+        <v>49</v>
+      </c>
+      <c r="H29" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J29" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L29" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="M29" s="10" t="str" cm="1">
+        <f t="array" ref="M29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A29)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N29" s="10" t="str" cm="1">
+        <f t="array" ref="N29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A29)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O29" s="10" t="str" cm="1">
+        <f t="array" ref="O29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A29)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P29" s="10" t="str" cm="1">
+        <f t="array" ref="P29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A29)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>15</v>
+      </c>
+      <c r="R29" s="10">
+        <v>25</v>
+      </c>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AA29" s="10"/>
+      <c r="AB29" s="10"/>
+    </row>
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M30, " mo, ",Sheet1!O30," KasaMath? Kuha ka na ng ", Sheet1!P30,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P30,"?**
+",Sheet2!E$17, Sheet1!Q30," days  
+- ", Sheet1!R30,"-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L30, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A30), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F30," para sa **", Sheet1!M30,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R30,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 7 KasaMath? Kuha ka na ng Standard Assessment Package!*
+**Bakit perfect para sa’yo ang Standard Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
+- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
+- Describe and explain the relationships between angle pairs based on their measures.
+- Classify polygons according to the number of sides, whether they are regular or irregular.
+- Classify polygons whether they are convex or non-convex.
+- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s1-sp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱79 para sa **First Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
 - **Table of Specifications**
   - XLSX format
 ---
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
       </c>
-      <c r="E29" s="10" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
+      <c r="E30" s="10"/>
+      <c r="F30" s="9">
+        <v>79</v>
+      </c>
+      <c r="G30" s="9">
+        <v>69</v>
+      </c>
+      <c r="H30" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L30" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="M30" s="10" t="str" cm="1">
+        <f t="array" ref="M30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A30)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N30" s="10" t="str" cm="1">
+        <f t="array" ref="N30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A30)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O30" s="10" t="str" cm="1">
+        <f t="array" ref="O30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A30)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P30" s="10" t="str" cm="1">
+        <f t="array" ref="P30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A30)),Sheet2!B$43:B$45,"")</f>
+        <v>Standard Assessment Package</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>15</v>
+      </c>
+      <c r="R30" s="10">
+        <v>25</v>
+      </c>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AA30" s="10"/>
+      <c r="AB30" s="10"/>
+    </row>
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M31, " mo, ",Sheet1!O31," KasaMath? Kuha ka na ng ", Sheet1!P31,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P31,"?**
+",Sheet2!F$17," 
+- Perfect sa teachers na gusto ng pasadyang exam", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L31, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A31), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F31," para sa **", Sheet1!M31,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R31,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 7 KasaMath? Kuha ka na ng Custom Assessment Package!*
+**Bakit perfect para sa’yo ang Custom Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang pwedeng covered
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50 
+- Perfect sa teachers na gusto ng pasadyang exam
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Draw and describe regular and irregular polygons with 5, 6, 8, or 10 sides, based on measurements of sides and angles, using a ruler and protractor.
+- Draw triangles, quadrilaterals, and regular polygons (5, 6, 8, or 10 sides) with given angle measures.
+- Describe and explain the relationships between angle pairs based on their measures.
+- Classify polygons according to the number of sides, whether they are regular or irregular.
+- Classify polygons whether they are convex or non-convex.
+- Deduce the relationship between the exterior angle and adjacent interior angle of a polygon.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s1-cp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱179 para sa **First Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="9">
+        <v>179</v>
+      </c>
+      <c r="G31" s="9">
+        <v>169</v>
+      </c>
+      <c r="H31" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J31" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="M31" s="10" t="str" cm="1">
+        <f t="array" ref="M31">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A31)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N31" s="10" t="str" cm="1">
+        <f t="array" ref="N31">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A31)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O31" s="10" t="str" cm="1">
+        <f t="array" ref="O31">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A31)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P31" s="10" t="str" cm="1">
+        <f t="array" ref="P31">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A31)),Sheet2!B$43:B$45,"")</f>
+        <v>Custom Assessment Package</v>
+      </c>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+      <c r="AA31" s="10"/>
+      <c r="AB31" s="10"/>
+    </row>
+    <row r="32" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M32, " mo, ",Sheet1!O32," KasaMath? Kuha ka na ng ", Sheet1!P32,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P32,"?**
+",Sheet2!D$17, Sheet1!Q32," days  
+- ", Sheet1!R32,"-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS", L32, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A32), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F32," para sa **", Sheet1!M32,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R32,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 7 KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
 - Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS
+---
+📑 **Competencies Covered**
+- Determine the measures of angles of polygons.
+- Determine the number of sides of polygons.
+- Solve problems involving percentage increase and percentage decrease.
+- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
+- Create a financial plan.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s2-bp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱59 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="9">
+        <v>59</v>
+      </c>
+      <c r="G32" s="9">
+        <v>49</v>
+      </c>
+      <c r="H32" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J32" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L32" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="M32" s="10" t="str" cm="1">
+        <f t="array" ref="M32">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A32)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N32" s="10" t="str" cm="1">
+        <f t="array" ref="N32">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A32)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O32" s="10" t="str" cm="1">
+        <f t="array" ref="O32">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A32)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P32" s="10" t="str" cm="1">
+        <f t="array" ref="P32">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A32)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>15</v>
+      </c>
+      <c r="R32" s="10">
+        <v>25</v>
+      </c>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+      <c r="AA32" s="10"/>
+      <c r="AB32" s="10"/>
+    </row>
+    <row r="33" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M33, " mo, ",Sheet1!O33," KasaMath? Kuha ka na ng ", Sheet1!P33,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P33,"?**
+",Sheet2!E$17, Sheet1!Q33," days  
+- ", Sheet1!R33,"-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L33, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A33), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F33," para sa **", Sheet1!M33,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R33,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 7 KasaMath? Kuha ka na ng Standard Assessment Package!*
+**Bakit perfect para sa’yo ang Standard Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Determine the measures of angles of polygons.
+- Determine the number of sides of polygons.
+- Solve problems involving percentage increase and percentage decrease.
+- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
+- Create a financial plan.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s2-sp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱79 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="9">
+        <v>79</v>
+      </c>
+      <c r="G33" s="9">
+        <v>69</v>
+      </c>
+      <c r="H33" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J33" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L33" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="M33" s="10" t="str" cm="1">
+        <f t="array" ref="M33">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A33)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N33" s="10" t="str" cm="1">
+        <f t="array" ref="N33">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A33)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O33" s="10" t="str" cm="1">
+        <f t="array" ref="O33">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A33)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P33" s="10" t="str" cm="1">
+        <f t="array" ref="P33">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A33)),Sheet2!B$43:B$45,"")</f>
+        <v>Standard Assessment Package</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>15</v>
+      </c>
+      <c r="R33" s="10">
+        <v>25</v>
+      </c>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
+    </row>
+    <row r="34" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M34, " mo, ",Sheet1!O34," KasaMath? Kuha ka na ng ", Sheet1!P34,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P34,"?**
+",Sheet2!F$17," 
+- Perfect sa teachers na gusto ng pasadyang exam", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L34, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A34), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F34," para sa **", Sheet1!M34,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R34,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 7 KasaMath? Kuha ka na ng Custom Assessment Package!*
+**Bakit perfect para sa’yo ang Custom Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang pwedeng covered
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50 
+- Perfect sa teachers na gusto ng pasadyang exam
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Determine the measures of angles of polygons.
+- Determine the number of sides of polygons.
+- Solve problems involving percentage increase and percentage decrease.
+- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
+- Create a financial plan.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-s2-cp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱179 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="9">
+        <v>179</v>
+      </c>
+      <c r="G34" s="9">
+        <v>169</v>
+      </c>
+      <c r="H34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J34" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="M34" s="10" t="str" cm="1">
+        <f t="array" ref="M34">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A34)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N34" s="10" t="str" cm="1">
+        <f t="array" ref="N34">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A34)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O34" s="10" t="str" cm="1">
+        <f t="array" ref="O34">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A34)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P34" s="10" t="str" cm="1">
+        <f t="array" ref="P34">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A34)),Sheet2!B$43:B$45,"")</f>
+        <v>Custom Assessment Package</v>
+      </c>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AA34" s="10"/>
+      <c r="AB34" s="10"/>
+    </row>
+    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="8" t="str">
+        <f>Sheet2!$D$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
 - Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
 - Maaga kang makakapag-submit ng TOS sa head mo.  
@@ -4969,7 +5771,7 @@
 ---
 ## Step 2: Payment and Delivery
 ### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
+Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
@@ -4991,267 +5793,54 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F29" s="9">
+      <c r="E35" s="4"/>
+      <c r="F35" s="9">
+        <v>120</v>
+      </c>
+      <c r="G35" s="9">
+        <v>84</v>
+      </c>
+      <c r="H35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="17">
+        <v>46176</v>
+      </c>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
+      <c r="AA35" s="10"/>
+      <c r="AB35" s="10"/>
+    </row>
+    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G29" s="9">
-        <v>50</v>
-      </c>
-      <c r="H29" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J29" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="17">
-        <v>46179</v>
-      </c>
-      <c r="L29" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="M29" s="10" t="str" cm="1">
-        <f t="array" ref="M29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A29)),Sheet2!B$23:B$26,"")</f>
-        <v>First Summative test</v>
-      </c>
-      <c r="N29" s="10" t="str" cm="1">
-        <f t="array" ref="N29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A29)),Sheet2!B$30:B$32,"")</f>
-        <v>First Term</v>
-      </c>
-      <c r="O29" s="10" t="str" cm="1">
-        <f t="array" ref="O29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A29)),Sheet2!B$36:B$39,"")</f>
-        <v>Grade 7</v>
-      </c>
-      <c r="P29" s="10" t="str" cm="1">
-        <f t="array" ref="P29">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A29)),Sheet2!B$43:B$45,"")</f>
-        <v>Basic Assessment Package</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>15</v>
-      </c>
-      <c r="R29" s="10">
-        <v>25</v>
-      </c>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10"/>
-      <c r="Z29" s="10"/>
-      <c r="AA29" s="10"/>
-      <c r="AB29" s="10"/>
-    </row>
-    <row r="30" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="8" t="str">
-        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M30, " mo, ",Sheet1!O30," KasaMath? Kuha ka na ng ", Sheet1!P30,"!*
-**Bakit perfect para sa’yo ang ", Sheet1!P30,"?**
-",Sheet2!D$17, L30, _xlfn._LONGTEXT("
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-M","ag-send ka lang ng ₱"),Sheet1!F30," para sa **", Sheet1!M30,_xlfn._LONGTEXT("**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: "), Sheet1!R30,"-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format", Sheet2!$D$6)</f>
-        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 7 KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: 15 days  
-- 25-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-📑 **Competencies Covered**
-- Determine the measures of angles of polygons.
-- Determine the number of sides of polygons.
-- Solve problems involving percentage increase and percentage decrease.
-- Solve money problems involving percentages (e. g., discount, commission, sales tax, simple interest).
-- Create a financial plan.
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱60 para sa **Second Summative test**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 25-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
-      </c>
-      <c r="E30" s="4" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F30" s="9">
-        <v>60</v>
-      </c>
-      <c r="G30" s="9">
-        <v>50</v>
-      </c>
-      <c r="H30" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="17">
-        <v>46179</v>
-      </c>
-      <c r="L30" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="M30" s="10" t="str" cm="1">
-        <f t="array" ref="M30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A30)),Sheet2!B$23:B$26,"")</f>
-        <v>Second Summative test</v>
-      </c>
-      <c r="N30" s="10" t="str" cm="1">
-        <f t="array" ref="N30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A30)),Sheet2!B$30:B$32,"")</f>
-        <v>First Term</v>
-      </c>
-      <c r="O30" s="10" t="str" cm="1">
-        <f t="array" ref="O30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A30)),Sheet2!B$36:B$39,"")</f>
-        <v>Grade 7</v>
-      </c>
-      <c r="P30" s="10" t="str" cm="1">
-        <f t="array" ref="P30">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A30)),Sheet2!B$43:B$45,"")</f>
-        <v>Basic Assessment Package</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>15</v>
-      </c>
-      <c r="R30" s="10">
-        <v>25</v>
-      </c>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10"/>
-      <c r="AB30" s="10"/>
-    </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="8" t="str">
+      <c r="C36" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5297,7 +5886,1126 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E31" s="4" t="str">
+      <c r="E36" s="4"/>
+      <c r="F36" s="15">
+        <v>165</v>
+      </c>
+      <c r="G36" s="15">
+        <v>115</v>
+      </c>
+      <c r="H36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="17">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="8" t="str">
+        <f>Sheet2!$F$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
+**Bakit perfect para sa’yo ang Premium Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Fully customizable exam: kahit anong topic ang pwedeng covered
+- Table of Specifications: pwedeng Bloom's format o 21st Century format
+- Number of days: pwede kahit ilan
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Perfect sa teachers na gusto ng pasadyang exam
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱350 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="15">
+        <v>350</v>
+      </c>
+      <c r="G37" s="15">
+        <v>245</v>
+      </c>
+      <c r="H37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M38, " mo, ",Sheet1!O38," KasaMath? Kuha ka na ng ", Sheet1!P38,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P38,"?**
+",Sheet2!D$17, Sheet1!Q38," days  
+- ", Sheet1!R38,"-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS", L38, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A38), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F38," para sa **", Sheet1!M38,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R38,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS
+---
+📑 **Competencies Covered**
+- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
+- Construct perpendicular and parallel lines.
+- Identify the relationships between angles formed by parallel lines cut by a transversal.
+- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
+- Identify relations that are functions based on the definitions of relations and functions.
+- Determine the domain and range of a function expressed in different representations.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s1-bp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱59 para sa **First Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="9">
+        <v>59</v>
+      </c>
+      <c r="G38" s="9">
+        <v>49</v>
+      </c>
+      <c r="H38" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J38" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L38" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="M38" s="10" t="str" cm="1">
+        <f t="array" ref="M38">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A38)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N38" s="10" t="str" cm="1">
+        <f t="array" ref="N38">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A38)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O38" s="10" t="str" cm="1">
+        <f t="array" ref="O38">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A38)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P38" s="10" t="str" cm="1">
+        <f t="array" ref="P38">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A38)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>15</v>
+      </c>
+      <c r="R38" s="10">
+        <v>25</v>
+      </c>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10"/>
+      <c r="AA38" s="10"/>
+      <c r="AB38" s="10"/>
+    </row>
+    <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D39" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M39, " mo, ",Sheet1!O39," KasaMath? Kuha ka na ng ", Sheet1!P39,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P39,"?**
+",Sheet2!E$17, Sheet1!Q39," days  
+- ", Sheet1!R39,"-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L39, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A39), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F39," para sa **", Sheet1!M39,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R39,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 9 KasaMath? Kuha ka na ng Standard Assessment Package!*
+**Bakit perfect para sa’yo ang Standard Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
+- Construct perpendicular and parallel lines.
+- Identify the relationships between angles formed by parallel lines cut by a transversal.
+- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
+- Identify relations that are functions based on the definitions of relations and functions.
+- Determine the domain and range of a function expressed in different representations.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s1-sp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱79 para sa **First Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="9">
+        <v>79</v>
+      </c>
+      <c r="G39" s="9">
+        <v>69</v>
+      </c>
+      <c r="H39" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J39" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L39" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="M39" s="10" t="str" cm="1">
+        <f t="array" ref="M39">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A39)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N39" s="10" t="str" cm="1">
+        <f t="array" ref="N39">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A39)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O39" s="10" t="str" cm="1">
+        <f t="array" ref="O39">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A39)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P39" s="10" t="str" cm="1">
+        <f t="array" ref="P39">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A39)),Sheet2!B$43:B$45,"")</f>
+        <v>Standard Assessment Package</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>15</v>
+      </c>
+      <c r="R39" s="10">
+        <v>25</v>
+      </c>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
+      <c r="Y39" s="10"/>
+      <c r="Z39" s="10"/>
+      <c r="AA39" s="10"/>
+      <c r="AB39" s="10"/>
+    </row>
+    <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M40, " mo, ",Sheet1!O40," KasaMath? Kuha ka na ng ", Sheet1!P40,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P40,"?**
+",Sheet2!F$17," 
+- Perfect sa teachers na gusto ng pasadyang exam", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L40, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A40), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F40," para sa **", Sheet1!M40,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R40,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 9 KasaMath? Kuha ka na ng Custom Assessment Package!*
+**Bakit perfect para sa’yo ang Custom Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang pwedeng covered
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50 
+- Perfect sa teachers na gusto ng pasadyang exam
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
+- Construct perpendicular and parallel lines.
+- Identify the relationships between angles formed by parallel lines cut by a transversal.
+- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
+- Identify relations that are functions based on the definitions of relations and functions.
+- Determine the domain and range of a function expressed in different representations.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s1-cp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱179 para sa **First Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="9">
+        <v>179</v>
+      </c>
+      <c r="G40" s="9">
+        <v>169</v>
+      </c>
+      <c r="H40" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J40" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L40" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="M40" s="10" t="str" cm="1">
+        <f t="array" ref="M40">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A40)),Sheet2!B$23:B$26,"")</f>
+        <v>First Summative test</v>
+      </c>
+      <c r="N40" s="10" t="str" cm="1">
+        <f t="array" ref="N40">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A40)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O40" s="10" t="str" cm="1">
+        <f t="array" ref="O40">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A40)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P40" s="10" t="str" cm="1">
+        <f t="array" ref="P40">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A40)),Sheet2!B$43:B$45,"")</f>
+        <v>Custom Assessment Package</v>
+      </c>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
+      <c r="AA40" s="10"/>
+      <c r="AB40" s="10"/>
+    </row>
+    <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D41" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M41, " mo, ",Sheet1!O41," KasaMath? Kuha ka na ng ", Sheet1!P41,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P41,"?**
+",Sheet2!D$17, Sheet1!Q41," days  
+- ", Sheet1!R41,"-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS", L41, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A41), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F41," para sa **", Sheet1!M41,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R41,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Para sa teachers na nagmamadali at hindi kailangan ang TOS
+---
+📑 **Competencies Covered**
+- Express the relationship between two variables as a function.
+- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
+- Graph a linear function and determine its domain, range, intercepts, and slope.
+- Represent linear relationships found in real-life situations using different representations.
+- Solve problems involving linear functions.
+- Determine conditions that guarantee parallelism and perpendicularity of lines.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s2-bp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱59 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="9">
+        <v>59</v>
+      </c>
+      <c r="G41" s="9">
+        <v>49</v>
+      </c>
+      <c r="H41" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J41" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="M41" s="10" t="str" cm="1">
+        <f t="array" ref="M41">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A41)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N41" s="10" t="str" cm="1">
+        <f t="array" ref="N41">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A41)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O41" s="10" t="str" cm="1">
+        <f t="array" ref="O41">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A41)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P41" s="10" t="str" cm="1">
+        <f t="array" ref="P41">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A41)),Sheet2!B$43:B$45,"")</f>
+        <v>Basic Assessment Package</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>15</v>
+      </c>
+      <c r="R41" s="10">
+        <v>25</v>
+      </c>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="10"/>
+      <c r="Y41" s="10"/>
+      <c r="Z41" s="10"/>
+      <c r="AA41" s="10"/>
+      <c r="AB41" s="10"/>
+    </row>
+    <row r="42" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D42" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M42, " mo, ",Sheet1!O42," KasaMath? Kuha ka na ng ", Sheet1!P42,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P42,"?**
+",Sheet2!E$17, Sheet1!Q42," days  
+- ", Sheet1!R42,"-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L42, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A42), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F42," para sa **", Sheet1!M42,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R42,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 9 KasaMath? Kuha ka na ng Standard Assessment Package!*
+**Bakit perfect para sa’yo ang Standard Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: 15 days  
+- 25-item Multiple Choice test with Answer Key  
+- Bagay sa teachers na gusto ng kumpletong exam, answer key, at TOS
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Express the relationship between two variables as a function.
+- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
+- Graph a linear function and determine its domain, range, intercepts, and slope.
+- Represent linear relationships found in real-life situations using different representations.
+- Solve problems involving linear functions.
+- Determine conditions that guarantee parallelism and perpendicularity of lines.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s2-sp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱79 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="9">
+        <v>79</v>
+      </c>
+      <c r="G42" s="9">
+        <v>69</v>
+      </c>
+      <c r="H42" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J42" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L42" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="M42" s="10" t="str" cm="1">
+        <f t="array" ref="M42">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A42)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N42" s="10" t="str" cm="1">
+        <f t="array" ref="N42">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A42)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O42" s="10" t="str" cm="1">
+        <f t="array" ref="O42">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A42)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P42" s="10" t="str" cm="1">
+        <f t="array" ref="P42">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A42)),Sheet2!B$43:B$45,"")</f>
+        <v>Standard Assessment Package</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>15</v>
+      </c>
+      <c r="R42" s="10">
+        <v>25</v>
+      </c>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="10"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
+      <c r="AA42" s="10"/>
+      <c r="AB42" s="10"/>
+    </row>
+    <row r="43" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D43" s="8" t="str">
+        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M43, " mo, ",Sheet1!O43," KasaMath? Kuha ka na ng ", Sheet1!P43,"!*
+**Bakit perfect para sa’yo ang ", Sheet1!P43,"?**
+",Sheet2!F$17," 
+- Perfect sa teachers na gusto ng pasadyang exam", _xlfn._LONGTEXT("
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted us","ing 21st Century Skills*"),L43, "
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+", "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A43), """ height=""850"" &gt;}}","
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱",Sheet1!F43," para sa **", Sheet1!M43,_xlfn._LONGTEXT("**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gm","ail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: "), Sheet1!R43,"-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format", Sheet2!$D$6)</f>
+        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 9 KasaMath? Kuha ka na ng Custom Assessment Package!*
+**Bakit perfect para sa’yo ang Custom Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang pwedeng covered
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50 
+- Perfect sa teachers na gusto ng pasadyang exam
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+📑 **Competencies Covered**
+- Express the relationship between two variables as a function.
+- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
+- Graph a linear function and determine its domain, range, intercepts, and slope.
+- Represent linear relationships found in real-life situations using different representations.
+- Solve problems involving linear functions.
+- Determine conditions that guarantee parallelism and perpendicularity of lines.
+---
+## Step 1: I-fill out at i-submit ang Order Form.
+{{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-s2-cp" height="850" &gt;}}
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱179 para sa **Second Summative test**. 
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 25-50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="9">
+        <v>179</v>
+      </c>
+      <c r="G43" s="9">
+        <v>169</v>
+      </c>
+      <c r="H43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" s="17">
+        <v>46179</v>
+      </c>
+      <c r="L43" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="M43" s="10" t="str" cm="1">
+        <f t="array" ref="M43">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A43)),Sheet2!B$23:B$26,"")</f>
+        <v>Second Summative test</v>
+      </c>
+      <c r="N43" s="10" t="str" cm="1">
+        <f t="array" ref="N43">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A43)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O43" s="10" t="str" cm="1">
+        <f t="array" ref="O43">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A43)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P43" s="10" t="str" cm="1">
+        <f t="array" ref="P43">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A43)),Sheet2!B$43:B$45,"")</f>
+        <v>Custom Assessment Package</v>
+      </c>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
+      <c r="Z43" s="10"/>
+      <c r="AA43" s="10"/>
+      <c r="AB43" s="10"/>
+    </row>
+    <row r="44" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="8" t="str">
+        <f>Sheet2!$D$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications (Bloom’s Taxonomy format)  
+- Number of days: 35 days  
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f>Sheet2!$A$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
+**Bakit perfect para sa’yo ang Basic Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Tipid din sa budget dahil naka-**30% discount**.
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications (Bloom’s Taxonomy format)  
+- Number of days: 35 days  
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Para sa teachers na nagmamadali  
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="F44" s="9">
+        <v>120</v>
+      </c>
+      <c r="G44" s="9">
+        <v>84</v>
+      </c>
+      <c r="H44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="17">
+        <v>46176</v>
+      </c>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="10"/>
+      <c r="X44" s="10"/>
+      <c r="Y44" s="10"/>
+      <c r="Z44" s="10"/>
+      <c r="AA44" s="10"/>
+      <c r="AB44" s="10"/>
+    </row>
+    <row r="45" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="8" t="str">
+        <f>Sheet2!$E$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
+**Bakit perfect para sa’yo ang Standard Assessment Package?**
+- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications: pwedeng Bloom's format o 21st Century format
+- Number of days: pwedeng 35 days o 40 days
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
+- Bagay sa teachers na gusto ng flexibility sa exam
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
+*Sample TOS formatted using 21st Century Skills*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
+---
+## Step 2: Payment and Delivery
+### Payment Methods
+Mag-send ka lang ng ₱165 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
+**Isend ang Screenshot ng Payment kahit saan dito:**
+- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
+- Facebook: https://m.me/jonathan.r.bacolod  
+- Telegram: https://t.me/Jonathan_Bacolod  
+Isesend ko ang files sa email address mo after ng payment. 
+### Delivery Includes:
+- **Test**
+  - Test type: 50-item multiple choice test
+  - Dimensions: A4 bond paper
+  - Format: PDF, created using LaTeX
+- **Answer Key**
+  - Format: PDF, created using LaTeX
+- **Table of Specifications**
+  - XLSX format
+---
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="E45" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5344,36 +7052,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F31" s="15">
+      <c r="F45" s="15">
         <v>165</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G45" s="15">
         <v>115</v>
       </c>
-      <c r="H31" s="4" t="b">
+      <c r="H45" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I45" s="5">
         <v>46176</v>
       </c>
-      <c r="J31" s="4" t="b">
+      <c r="J45" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K45" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="8" t="str">
+    <row r="46" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5419,7 +7127,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E32" s="4" t="str">
+      <c r="E46" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5466,36 +7174,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F32" s="15">
+      <c r="F46" s="15">
         <v>350</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G46" s="15">
         <v>245</v>
       </c>
-      <c r="H32" s="4" t="b">
+      <c r="H46" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I46" s="5">
         <v>46176</v>
       </c>
-      <c r="J32" s="4" t="b">
+      <c r="J46" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K46" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="8" t="str">
+    <row r="47" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5539,7 +7247,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E33" s="4" t="str">
+      <c r="E47" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -5584,53 +7292,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F33" s="9">
+      <c r="F47" s="9">
         <v>120</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G47" s="9">
         <v>84</v>
       </c>
-      <c r="H33" s="4" t="b">
+      <c r="H47" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I47" s="5">
         <v>46176</v>
       </c>
-      <c r="J33" s="4" t="b">
+      <c r="J47" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K47" s="17">
         <v>46176</v>
       </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10"/>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10"/>
-      <c r="AA33" s="10"/>
-      <c r="AB33" s="10"/>
-    </row>
-    <row r="34" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="8" t="str">
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
+      <c r="X47" s="10"/>
+      <c r="Y47" s="10"/>
+      <c r="Z47" s="10"/>
+      <c r="AA47" s="10"/>
+      <c r="AB47" s="10"/>
+    </row>
+    <row r="48" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5676,7 +7384,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E34" s="4" t="str">
+      <c r="E48" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -5723,36 +7431,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F34" s="15">
+      <c r="F48" s="15">
         <v>165</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G48" s="15">
         <v>115</v>
       </c>
-      <c r="H34" s="4" t="b">
+      <c r="H48" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I48" s="5">
         <v>46176</v>
       </c>
-      <c r="J34" s="4" t="b">
+      <c r="J48" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K48" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="13" t="s">
+    <row r="49" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="8" t="str">
+      <c r="D49" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5798,7 +7506,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E35" s="4" t="str">
+      <c r="E49" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -5845,114 +7553,69 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F35" s="15">
+      <c r="F49" s="15">
         <v>350</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G49" s="15">
         <v>245</v>
       </c>
-      <c r="H35" s="4" t="b">
+      <c r="H49" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I49" s="5">
         <v>46176</v>
       </c>
-      <c r="J35" s="4" t="b">
+      <c r="J49" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K49" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="D36" s="8" t="str">
-        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M36, " mo, ",Sheet1!O36," KasaMath? Kuha ka na ng ", Sheet1!P36,"!*
-**Bakit perfect para sa’yo ang ", Sheet1!P36,"?**
-",Sheet2!D$17, L36, _xlfn._LONGTEXT("
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-M","ag-send ka lang ng ₱"),Sheet1!F36," para sa **", Sheet1!M36,_xlfn._LONGTEXT("**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: "), Sheet1!R36,"-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format", Sheet2!$D$6)</f>
-        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at First Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
+    <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="8" t="str">
+        <f>Sheet2!$D$2</f>
+        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
 - Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
 - Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
 - Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: 15 days  
-- 25-item Multiple Choice test with Answer Key  
+- Ready-to-print exam: buong term ang covered topics  
+- Table of Specifications (Bloom’s Taxonomy format)  
+- Number of days: 35 days  
+- 50-item Multiple Choice test with Answer Key  
+- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
 - Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-📑 **Competencies Covered**
-- Illustrate and describe point, line, ray, line segment, angle, and plane using models and geometric notations.
-- Construct perpendicular and parallel lines.
-- Identify the relationships between angles formed by parallel lines cut by a transversal.
-- Determine angle measures involving angle pairs, parallel and perpendicular lines, and parallel lines cut by a transversal.
-- Identify relations that are functions based on the definitions of relations and functions.
-- Determine the domain and range of a function expressed in different representations.
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
+[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
+*Sample TOS formatted using Bloom’s Taxonomy*
+---
+## Step 1: I-fill out at i-submit ang Order Form
+{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
 ---
 ## Step 2: Payment and Delivery
 ### Payment Methods
-Mag-send ka lang ng ₱60 para sa **First Summative test**. 
+Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
 - **Landbank**: 0695077289 (Jonathan R. Bacolod)  
 - **GCash**: 09128389571 (Jonathan Bacolod)  
 - **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
+**Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
 ### Delivery Includes:
 - **Test**
-  - Test type: 25-item multiple choice test
+  - Test type: 50-item multiple choice test
   - Dimensions: A4 bond paper
   - Format: PDF, created using LaTeX
 - **Answer Key**
@@ -5960,9 +7623,10 @@
 - **Table of Specifications**
   - XLSX format
 ---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
-      </c>
-      <c r="E36" s="10" t="str">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
+</v>
+      </c>
+      <c r="E50" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6007,268 +7671,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F36" s="9">
-        <v>60</v>
-      </c>
-      <c r="G36" s="9">
-        <v>50</v>
-      </c>
-      <c r="H36" s="10" t="b">
+      <c r="F50" s="9">
+        <v>120</v>
+      </c>
+      <c r="G50" s="9">
+        <v>84</v>
+      </c>
+      <c r="H50" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I50" s="5">
         <v>46176</v>
       </c>
-      <c r="J36" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="17">
-        <v>46179</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="M36" s="10" t="str" cm="1">
-        <f t="array" ref="M36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A36)),Sheet2!B$23:B$26,"")</f>
-        <v>First Summative test</v>
-      </c>
-      <c r="N36" s="10" t="str" cm="1">
-        <f t="array" ref="N36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A36)),Sheet2!B$30:B$32,"")</f>
-        <v>First Term</v>
-      </c>
-      <c r="O36" s="10" t="str" cm="1">
-        <f t="array" ref="O36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A36)),Sheet2!B$36:B$39,"")</f>
-        <v>Grade 9</v>
-      </c>
-      <c r="P36" s="10" t="str" cm="1">
-        <f t="array" ref="P36">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A36)),Sheet2!B$43:B$45,"")</f>
-        <v>Basic Assessment Package</v>
-      </c>
-      <c r="Q36" s="10">
-        <v>15</v>
-      </c>
-      <c r="R36" s="10">
-        <v>25</v>
-      </c>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10"/>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
-      <c r="AA36" s="10"/>
-      <c r="AB36" s="10"/>
-    </row>
-    <row r="37" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="D37" s="8" t="str">
-        <f>CONCATENATE("*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at ", Sheet1!M37, " mo, ",Sheet1!O37," KasaMath? Kuha ka na ng ", Sheet1!P37,"!*
-**Bakit perfect para sa’yo ang ", Sheet1!P37,"?**
-",Sheet2!D$17, L37, _xlfn._LONGTEXT("
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-M","ag-send ka lang ng ₱"),Sheet1!F37," para sa **", Sheet1!M37,_xlfn._LONGTEXT("**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto",":texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: "), Sheet1!R37,"-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format", Sheet2!$D$6)</f>
-        <v>*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at Second Summative test mo, Grade 9 KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: 15 days  
-- 25-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-📑 **Competencies Covered**
-- Express the relationship between two variables as a function.
-- Determine the slopes (as rate of change) and zeros of linear functions represented in graphs, equations, and tables of values.
-- Graph a linear function and determine its domain, range, intercepts, and slope.
-- Represent linear relationships found in real-life situations using different representations.
-- Solve problems involving linear functions.
-- Determine conditions that guarantee parallelism and perpendicularity of lines.
----
-## Step 1: I-fill out at i-submit ang Order Form thru email, Messenger, or Telegram.
-- Name:
-- Email address:
-- Grade level:
-- Region:
-- Division:
-- Name of School:
-- Address of School:
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱60 para sa **Second Summative test**. 
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Order Form at Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 25-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com).</v>
-      </c>
-      <c r="E37" s="4" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F37" s="9">
-        <v>60</v>
-      </c>
-      <c r="G37" s="9">
-        <v>50</v>
-      </c>
-      <c r="H37" s="4" t="b">
+      <c r="J50" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="K50" s="17">
         <v>46176</v>
       </c>
-      <c r="J37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="17">
-        <v>46179</v>
-      </c>
-      <c r="L37" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="M37" s="10" t="str" cm="1">
-        <f t="array" ref="M37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A37)),Sheet2!B$23:B$26,"")</f>
-        <v>Second Summative test</v>
-      </c>
-      <c r="N37" s="10" t="str" cm="1">
-        <f t="array" ref="N37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A37)),Sheet2!B$30:B$32,"")</f>
-        <v>First Term</v>
-      </c>
-      <c r="O37" s="10" t="str" cm="1">
-        <f t="array" ref="O37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A37)),Sheet2!B$36:B$39,"")</f>
-        <v>Grade 9</v>
-      </c>
-      <c r="P37" s="10" t="str" cm="1">
-        <f t="array" ref="P37">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A37)),Sheet2!B$43:B$45,"")</f>
-        <v>Basic Assessment Package</v>
-      </c>
-      <c r="Q37" s="10">
-        <v>15</v>
-      </c>
-      <c r="R37" s="10">
-        <v>25</v>
-      </c>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="10"/>
-      <c r="AB37" s="10"/>
-    </row>
-    <row r="38" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13" t="s">
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
+      <c r="X50" s="10"/>
+      <c r="Y50" s="10"/>
+      <c r="Z50" s="10"/>
+      <c r="AA50" s="10"/>
+      <c r="AB50" s="10"/>
+    </row>
+    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="8" t="str">
+      <c r="D51" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6314,7 +7763,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E38" s="4" t="str">
+      <c r="E51" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6361,36 +7810,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F38" s="15">
+      <c r="F51" s="15">
         <v>165</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G51" s="15">
         <v>115</v>
       </c>
-      <c r="H38" s="4" t="b">
+      <c r="H51" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I51" s="5">
         <v>46176</v>
       </c>
-      <c r="J38" s="4" t="b">
+      <c r="J51" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K38" s="17">
+      <c r="K51" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13" t="s">
+    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="8" t="str">
+      <c r="C52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6436,7 +7885,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E39" s="4" t="str">
+      <c r="E52" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6483,36 +7932,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F39" s="15">
+      <c r="F52" s="15">
         <v>350</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G52" s="15">
         <v>245</v>
       </c>
-      <c r="H39" s="4" t="b">
+      <c r="H52" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I52" s="5">
         <v>46176</v>
       </c>
-      <c r="J39" s="4" t="b">
+      <c r="J52" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K52" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13" t="s">
+    <row r="53" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="8" t="str">
+      <c r="D53" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6556,7 +8005,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E40" s="4" t="str">
+      <c r="E53" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6601,53 +8050,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F40" s="9">
+      <c r="F53" s="9">
         <v>120</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G53" s="9">
         <v>84</v>
       </c>
-      <c r="H40" s="4" t="b">
+      <c r="H53" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I53" s="5">
         <v>46176</v>
       </c>
-      <c r="J40" s="4" t="b">
+      <c r="J53" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K40" s="17">
+      <c r="K53" s="17">
         <v>46176</v>
       </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10"/>
-      <c r="Y40" s="10"/>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="10"/>
-      <c r="AB40" s="10"/>
-    </row>
-    <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="8" t="str">
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
+      <c r="AA53" s="10"/>
+      <c r="AB53" s="10"/>
+    </row>
+    <row r="54" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6693,7 +8142,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E41" s="4" t="str">
+      <c r="E54" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -6740,36 +8189,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F41" s="15">
+      <c r="F54" s="15">
         <v>165</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G54" s="15">
         <v>115</v>
       </c>
-      <c r="H41" s="4" t="b">
+      <c r="H54" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I54" s="5">
         <v>46176</v>
       </c>
-      <c r="J41" s="4" t="b">
+      <c r="J54" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K41" s="17">
+      <c r="K54" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="20" t="s">
+    <row r="55" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="8" t="str">
+      <c r="C55" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6815,7 +8264,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E42" s="4" t="str">
+      <c r="E55" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -6862,36 +8311,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F42" s="15">
+      <c r="F55" s="15">
         <v>350</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G55" s="15">
         <v>245</v>
       </c>
-      <c r="H42" s="4" t="b">
+      <c r="H55" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I55" s="5">
         <v>46176</v>
       </c>
-      <c r="J42" s="4" t="b">
+      <c r="J55" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K42" s="17">
+      <c r="K55" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="8" t="str">
+    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6935,7 +8384,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E43" s="4" t="str">
+      <c r="E56" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -6980,53 +8429,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F43" s="9">
+      <c r="F56" s="9">
         <v>120</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G56" s="9">
         <v>84</v>
       </c>
-      <c r="H43" s="4" t="b">
+      <c r="H56" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I56" s="5">
         <v>46176</v>
       </c>
-      <c r="J43" s="4" t="b">
+      <c r="J56" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K43" s="17">
+      <c r="K56" s="17">
         <v>46176</v>
       </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10"/>
-      <c r="Y43" s="10"/>
-      <c r="Z43" s="10"/>
-      <c r="AA43" s="10"/>
-      <c r="AB43" s="10"/>
-    </row>
-    <row r="44" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="8" t="str">
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+      <c r="Z56" s="10"/>
+      <c r="AA56" s="10"/>
+      <c r="AB56" s="10"/>
+    </row>
+    <row r="57" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7072,7 +8521,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E44" s="4" t="str">
+      <c r="E57" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -7119,36 +8568,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F44" s="15">
+      <c r="F57" s="15">
         <v>165</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G57" s="15">
         <v>115</v>
       </c>
-      <c r="H44" s="4" t="b">
+      <c r="H57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I57" s="5">
         <v>46176</v>
       </c>
-      <c r="J44" s="4" t="b">
+      <c r="J57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K44" s="17">
+      <c r="K57" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" s="8" t="str">
+    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7194,7 +8643,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E45" s="4" t="str">
+      <c r="E58" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -7241,1178 +8690,44 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F45" s="15">
+      <c r="F58" s="15">
         <v>350</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G58" s="15">
         <v>245</v>
       </c>
-      <c r="H45" s="4" t="b">
+      <c r="H58" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I58" s="5">
         <v>46176</v>
       </c>
-      <c r="J45" s="4" t="b">
+      <c r="J58" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K45" s="17">
+      <c r="K58" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="8" t="str">
-        <f>Sheet2!$D$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E46" s="4" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F46" s="9">
-        <v>120</v>
-      </c>
-      <c r="G46" s="9">
-        <v>84</v>
-      </c>
-      <c r="H46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" s="17">
-        <v>46176</v>
-      </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="10"/>
-      <c r="AB46" s="10"/>
-    </row>
-    <row r="47" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D47" s="8" t="str">
-        <f>Sheet2!$E$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱165 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E47" s="4" t="str">
-        <f>Sheet2!$B$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱115 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F47" s="15">
-        <v>165</v>
-      </c>
-      <c r="G47" s="15">
-        <v>115</v>
-      </c>
-      <c r="H47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="8" t="str">
-        <f>Sheet2!$F$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱350 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E48" s="4" t="str">
-        <f>Sheet2!$C$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱245 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F48" s="15">
-        <v>350</v>
-      </c>
-      <c r="G48" s="15">
-        <v>245</v>
-      </c>
-      <c r="H48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="8" t="str">
-        <f>Sheet2!$D$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E49" s="4" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F49" s="9">
-        <v>120</v>
-      </c>
-      <c r="G49" s="9">
-        <v>84</v>
-      </c>
-      <c r="H49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" s="17">
-        <v>46176</v>
-      </c>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="X49" s="10"/>
-      <c r="Y49" s="10"/>
-      <c r="Z49" s="10"/>
-      <c r="AA49" s="10"/>
-      <c r="AB49" s="10"/>
-    </row>
-    <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="8" t="str">
-        <f>Sheet2!$E$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱165 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E50" s="4" t="str">
-        <f>Sheet2!$B$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱115 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F50" s="15">
-        <v>165</v>
-      </c>
-      <c r="G50" s="15">
-        <v>115</v>
-      </c>
-      <c r="H50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="8" t="str">
-        <f>Sheet2!$F$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱350 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E51" s="4" t="str">
-        <f>Sheet2!$C$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱245 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F51" s="15">
-        <v>350</v>
-      </c>
-      <c r="G51" s="15">
-        <v>245</v>
-      </c>
-      <c r="H51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="8" t="str">
-        <f>Sheet2!$D$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱120 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E52" s="4" t="str">
-        <f>Sheet2!$A$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Basic Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications (Bloom’s Taxonomy format)  
-- Number of days: 35 days  
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱84 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F52" s="9">
-        <v>120</v>
-      </c>
-      <c r="G52" s="9">
-        <v>84</v>
-      </c>
-      <c r="H52" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J52" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" s="17">
-        <v>46176</v>
-      </c>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="10"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-      <c r="Y52" s="10"/>
-      <c r="Z52" s="10"/>
-      <c r="AA52" s="10"/>
-      <c r="AB52" s="10"/>
-    </row>
-    <row r="53" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" s="8" t="str">
-        <f>Sheet2!$E$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱165 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E53" s="4" t="str">
-        <f>Sheet2!$B$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Standard Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: buong term ang covered topics  
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwedeng 35 days o 40 days
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Bagay sa teachers na gusto ng flexibility sa exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱115 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F53" s="15">
-        <v>165</v>
-      </c>
-      <c r="G53" s="15">
-        <v>115</v>
-      </c>
-      <c r="H53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D54" s="8" t="str">
-        <f>Sheet2!$F$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱350 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**.
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="E54" s="4" t="str">
-        <f>Sheet2!$C$2</f>
-        <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
-**Bakit perfect para sa’yo ang Premium Assessment Package?**
-- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
-- Tipid din sa budget dahil naka-**30% discount**.
-- Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo.  
-- Fully customizable exam: kahit anong topic ang pwedeng covered
-- Table of Specifications: pwedeng Bloom's format o 21st Century format
-- Number of days: pwede kahit ilan
-- 50-item Multiple Choice test with Answer Key  
-- Add ka lang ng ₱80 kung gusto mo idagdag ang **Periodic Test**  
-- Perfect sa teachers na gusto ng pasadyang exam
-[![Sample TOS formatted using Bloom’s Taxonomy](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351319/vb4ulrsvcgdxqwn7fdha.png)
-*Sample TOS formatted using Bloom’s Taxonomy*
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*
----
-## Step 1: I-fill out at i-submit ang Order Form
-{{&lt; iframe src="https://cityofsmiles.github.io/texmathpro-order-taker/" height="850" &gt;}}
----
-## Step 2: Payment and Delivery
-### Payment Methods
-Mag-send ka lang ng ₱245 para sa **First Summative test**. Magdagdag ka lang ng ₱80 kung gusto mo ring isama ang **Periodic Test**. Sulitin mo na ang **Early Bird Promo**, KasaMath!
-- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
-- **GCash**: 09128389571 (Jonathan Bacolod)  
-- **Maya**: 09128389571 (Jonathan Bacolod)  
-**Isend ang Screenshot ng Payment kahit saan dito:**
-- Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
-- Facebook: https://m.me/jonathan.r.bacolod  
-- Telegram: https://t.me/Jonathan_Bacolod  
-Isesend ko ang files sa email address mo after ng payment. 
-### Delivery Includes:
-- **Test**
-  - Test type: 50-item multiple choice test
-  - Dimensions: A4 bond paper
-  - Format: PDF, created using LaTeX
-- **Answer Key**
-  - Format: PDF, created using LaTeX
-- **Table of Specifications**
-  - XLSX format
----
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
-</v>
-      </c>
-      <c r="F54" s="15">
-        <v>350</v>
-      </c>
-      <c r="G54" s="15">
-        <v>245</v>
-      </c>
-      <c r="H54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" s="17">
-        <v>46176</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D55" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F55/10," Multiple-choice Quizzes |
+    <row r="59" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, S59," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H55, G55, F55),"|", CHAR(10), CHAR(10),CHAR(10), L55, CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A55), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
-        <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
+| Price | ₱",IF(H59, G59, F59),"|", CHAR(10), CHAR(10),CHAR(10), L59, CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A59), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10),"---
+🛒 **Payment Methods**
+Mag-send ka lang ng ₱",Sheet1!F59," para sa **", Sheet1!M59,"**.
+", Sheet2!$B$6)</f>
+        <v>Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
@@ -8426,7 +8741,7 @@
 | Content |9 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱90|
+| Price | ₱89|
 ---
 📑 **Topics Covered**
 **Quiz 1.01.1: Drawing Polygons by Side and Angle Measurements** (35 items)
@@ -8467,75 +8782,87 @@
 {{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g7-t1-mq" height="850" &gt;}}
 ---
 🛒 **Payment Methods**
-| Method | Account Details | Payment Amount |
-|---|---|---|
-| 💳 ATM (Landbank) | 0695077289 | Exact Amount |
-| 💸 GCash | 09128389571 | Add ₱15 convenience fee |
-| 💸 Maya | 09128389571 | Add ₱15 convenience fee |
+Mag-send ka lang ng ₱89 para sa **Multiple-choice Quizzes**.
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
 **Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
 ---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
-</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="9">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/).</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="9">
+        <v>89</v>
+      </c>
+      <c r="G59" s="9">
+        <v>79</v>
+      </c>
+      <c r="H59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" s="17">
+        <v>46176</v>
+      </c>
+      <c r="L59" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="M59" s="10" t="str" cm="1">
+        <f t="array" ref="M59">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A59)),Sheet2!B$23:B$26,"")</f>
+        <v>Multiple-choice Quizzes</v>
+      </c>
+      <c r="N59" s="10" t="str" cm="1">
+        <f t="array" ref="N59">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A59)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O59" s="10" t="str" cm="1">
+        <f t="array" ref="O59">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A59)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 7</v>
+      </c>
+      <c r="P59" s="10" t="str" cm="1">
+        <f t="array" ref="P59">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A59)),Sheet2!B$43:B$45,"")</f>
+        <v/>
+      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10">
+        <v>9</v>
+      </c>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
+      <c r="X59" s="10"/>
+      <c r="Y59" s="10"/>
+      <c r="Z59" s="10"/>
+      <c r="AA59" s="10"/>
+      <c r="AB59" s="10"/>
+    </row>
+    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G55" s="9">
-        <v>80</v>
-      </c>
-      <c r="H55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K55" s="17">
-        <v>46176</v>
-      </c>
-      <c r="L55" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="10"/>
-      <c r="Y55" s="10"/>
-      <c r="Z55" s="10"/>
-      <c r="AA55" s="10"/>
-      <c r="AB55" s="10"/>
-    </row>
-    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F56/25," Multiple-choice Quizzes |
+      <c r="D60" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F60/25," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H56, G56, F56),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A56), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L56, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
-        <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
+| Price | ₱",IF(H60, G60, F60),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A60), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L60, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+        <v>Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
@@ -8589,75 +8916,73 @@
 **Quiz 1.6: Finding Patterns in Sequences** (30 items)
   - Lesson 1.13.1: Finding Patterns in Arithmetic Sequences
   - Lesson 1.13.2: Finding Patterns in Geometric Sequences
----
-🛒 **Payment Methods**
-| Method | Account Details | Payment Amount |
-|---|---|---|
-| 💳 ATM (Landbank) | 0695077289 | Exact Amount |
-| 💸 GCash | 09128389571 | Add ₱15 convenience fee |
-| 💸 Maya | 09128389571 | Add ₱15 convenience fee |
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
 **Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
 ---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
-</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="9">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/).</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="9">
         <v>150</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="4" t="b">
+      <c r="G60" s="9"/>
+      <c r="H60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I60" s="5">
         <v>46176</v>
       </c>
-      <c r="J56" s="4" t="b">
+      <c r="J60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K56" s="17">
+      <c r="K60" s="17">
         <v>46176</v>
       </c>
-      <c r="L56" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="10"/>
-      <c r="AA56" s="10"/>
-      <c r="AB56" s="10"/>
-    </row>
-    <row r="57" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F57/25," Multiple-choice Quizzes |
+      <c r="L60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
+      <c r="X60" s="10"/>
+      <c r="Y60" s="10"/>
+      <c r="Z60" s="10"/>
+      <c r="AA60" s="10"/>
+      <c r="AB60" s="10"/>
+    </row>
+    <row r="61" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="D61" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, S61," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H57, G57, F57),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A57), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L57, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
-        <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
+| Price | ₱",IF(H61, G61, F61),"|", CHAR(10), CHAR(10),CHAR(10), L61, CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A61), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10),"---
+🛒 **Payment Methods**
+Mag-send ka lang ng ₱",Sheet1!F61," para sa **", Sheet1!M61,"**.
+", Sheet2!$B$6)</f>
+        <v>Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
@@ -8668,80 +8993,137 @@
  📑 **Product Details**
 | Feature | Details |
 |---|---|
-| Content |4 Multiple-choice Quizzes |
+| Content |10 Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱100|
+| Price | ₱99|
+---
+📑 **Topics Covered**
+**Quiz 1.01.1: Basic Undefined Terms and Geometric Notation** (35 items)
+  - Lesson 1. 1.01.1: Basic Undefined Terms and Geometric Notation
+  - Lesson 1. 1.01.2: Constructing Parallel and Perpendicular Lines
+**Quiz 1.02.1: Angles Formed by Parallel Lines and a Transversal** (30 items)
+  - Lesson 1. 1.02.1: Angles Formed by Parallel Lines and a Transversal
+  - Lesson 1. 1.02.2: Solving Angle Measures with Parallel and Perpendicular Lines
+**Quiz 1.03.1: Introduction to Relations and Functions** (30 items)
+  - Lesson 1. 1.03.1: Introduction to Relations and Functions
+  - Lesson 1. 1.03.2: Domain of a Function
+  - Lesson 1. 1.03.3: Range of a Function
+**Quiz 1.04.1: Representing Relationships as Functions** (30 items)
+  - Lesson 1. 1.04.1: Representing Relationships as Functions
+  - Lesson 1. 1.04.2: Slope of Linear Functions from Graphs
+  - Lesson 1. 1.04.3: Zeros of Linear Functions from Graphs
+  - Lesson 1. 1.04.4: Slope of Linear Functions from Equations
+  - Lesson 1. 1.04.5: Zeros of Linear Functions from Equations
+  - Lesson 1. 1.04.6: Slope of Linear Functions from Tables
+  - Lesson 1. 1.04.7: Zeros of Linear Functions from Tables
+**Quiz 1.05.1: Graphing Linear Functions: Domain and Range** (35 items)
+  - Lesson 1. 1.05.1: Graphing Linear Functions: Domain and Range
+  - Lesson 1. 1.05.2: Graphing Linear Function - Intercepts and Slope
+  - Lesson 1. 1.05.3: Representing Real-Life Linear Relationships
+**Quiz 1.06.1: Solving Problems Involving Linear Functions** (30 items)
+  - Lesson 1. 1.06.1: Solving Problems Involving Linear Functions
+  - Lesson 1. 1.06.2: Conditions that Guarantee Parallelism
+  - Lesson 1. 1.06.3: Conditions that Guarantee Perpendicularity
+**Quiz 1.07.1: Classifying Quadrilaterals** (35 items)
+  - Lesson 1. 1.07.1: Classifying Quadrilaterals
+  - Lesson 1. 1.07.2: Properties of Parallelograms
+**Quiz 1.08.1: Finding Lengths in Parallelograms** (30 items)
+  - Lesson 1. 1.08.1: Finding Side Lengths in Parallelograms
+  - Lesson 1. 1.08.2: Finding Angle Measures in Parallelograms
+  - Lesson 1. 1.08.3: Finding Perpendicular Heights in Parallelograms
+  - Lesson 1. 1.08.4: Finding Diagonal Measures in Parallelograms
+**Quiz 1.09.1: Problem Solving with Parallelograms** (30 items)
+  - Lesson 1. 1.09.1: Problem Solving with Parallelograms and Rectangles
+  - Lesson 1. 1.09.2: Problem Solving with Squares and Rhombuses
+**Quiz 1.10.1: Proving Properties of Parallelograms** (25 items)
+  - Lesson 1. 1.10.1: Proving Properties of Parallelograms
 ---
 📥 **I-fill out ang Order Form**
 {{&lt; iframe src="https://cityofsmiles.github.io/auto-order-form/?id=g9-t1-mq" height="850" &gt;}}
 ---
 🛒 **Payment Methods**
-| Method | Account Details | Payment Amount |
-|---|---|---|
-| 💳 ATM (Landbank) | 0695077289 | Exact Amount |
-| 💸 GCash | 09128389571 | Add ₱15 convenience fee |
-| 💸 Maya | 09128389571 | Add ₱15 convenience fee |
+Mag-send ka lang ng ₱99 para sa **Multiple-choice Quizzes**.
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
 **Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
 ---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
-</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="9">
-        <v>100</v>
-      </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="4" t="b">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/).</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="9">
+        <v>99</v>
+      </c>
+      <c r="G61" s="9">
+        <v>89</v>
+      </c>
+      <c r="H61" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I61" s="5">
         <v>46176</v>
       </c>
-      <c r="J57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" s="17">
+      <c r="J61" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" s="17">
         <v>46176</v>
       </c>
-      <c r="L57" s="4"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
-      <c r="X57" s="10"/>
-      <c r="Y57" s="10"/>
-      <c r="Z57" s="10"/>
-      <c r="AA57" s="10"/>
-      <c r="AB57" s="10"/>
-    </row>
-    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58" s="8" t="str">
-        <f>CONCATENATE(Sheet2!$C$6, F58/25," Multiple-choice Quizzes |
+      <c r="L61" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="M61" s="10" t="str" cm="1">
+        <f t="array" ref="M61">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$23:A$26,A61)),Sheet2!B$23:B$26,"")</f>
+        <v>Multiple-choice Quizzes</v>
+      </c>
+      <c r="N61" s="10" t="str" cm="1">
+        <f t="array" ref="N61">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$30:A$32,A61)),Sheet2!B$30:B$32,"")</f>
+        <v>First Term</v>
+      </c>
+      <c r="O61" s="10" t="str" cm="1">
+        <f t="array" ref="O61">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$36:A$39,A61)),Sheet2!B$36:B$39,"")</f>
+        <v>Grade 9</v>
+      </c>
+      <c r="P61" s="10" t="str" cm="1">
+        <f t="array" ref="P61">_xlfn.XLOOKUP(TRUE,ISNUMBER(SEARCH(Sheet2!A$43:A$45,A61)),Sheet2!B$43:B$45,"")</f>
+        <v/>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10">
+        <v>10</v>
+      </c>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
+      <c r="Z61" s="10"/>
+      <c r="AA61" s="10"/>
+      <c r="AB61" s="10"/>
+    </row>
+    <row r="62" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" s="8" t="str">
+        <f>CONCATENATE(Sheet2!$C$6, F62/25," Multiple-choice Quizzes |
 | Paper Size | A4 Bond Paper |
 | File Format | PDF (Typeset in LaTeX) |
-| Price | ₱",IF(H58, G58, F58),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A58), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L58, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
-        <v xml:space="preserve">Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
+| Price | ₱",IF(H62, G62, F62),"|", CHAR(10),CHAR(10),CHAR(10), "---",CHAR(10),CHAR(10), "📥 **I-fill out ang Order Form**",CHAR(10),CHAR(10), "{{&lt; iframe src=""", "https://cityofsmiles.github.io/auto-order-form/?id=", LOWER(A62), """ height=""850"" &gt;}}", CHAR(10), CHAR(10),CHAR(10), L62, CHAR(10), CHAR(10),CHAR(10), Sheet2!$B$6)</f>
+        <v>Tinatamad ka ba, walang time, o nahihirapang gumawa ng quizzes mo this term, KasaMath? 
 ✨  Kuha ka na ng Multiple Choice Quizzes with Answer Keys para:
  - Tipid ka sa oras at makapag-focus sa pagtuturo. 
  - Maganda at consistent ang formatting ng test questions at figures mo. 
@@ -8798,74 +9180,69 @@
   - Lesson 1.12.3: Solving Polynomial Equations of Degree Greater than 2
   - Lesson 1.13.1: Solving Problems Involving Polynomials
   - Lesson 1.13.2: Solving Problems Involving Polynomial Equations
----
-🛒 **Payment Methods**
-| Method | Account Details | Payment Amount |
-|---|---|---|
-| 💳 ATM (Landbank) | 0695077289 | Exact Amount |
-| 💸 GCash | 09128389571 | Add ₱15 convenience fee |
-| 💸 Maya | 09128389571 | Add ₱15 convenience fee |
+- **Landbank**: 0695077289 (Jonathan R. Bacolod)  
+- **GCash**: 09128389571 (Jonathan Bacolod)  
+- **Maya**: 09128389571 (Jonathan Bacolod)  
 **Isend ang Screenshot ng Payment kahit saan dito:**
 - Email: [texmathpro@gmail.com](mailto:texmathpro@gmail.com)  
 - Facebook: https://m.me/jonathan.r.bacolod  
 - Telegram: https://t.me/Jonathan_Bacolod  
 Isesend ko ang files sa email address mo after ng payment. 
 ---
-Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/). 
-</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="9">
+Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](https://texmathpro.github.io/contact/).</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="9">
         <v>100</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="4" t="b">
+      <c r="G62" s="9"/>
+      <c r="H62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I62" s="5">
         <v>46176</v>
       </c>
-      <c r="J58" s="4" t="b">
+      <c r="J62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K58" s="17">
+      <c r="K62" s="17">
         <v>46176</v>
       </c>
-      <c r="L58" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="10"/>
-      <c r="S58" s="10"/>
-      <c r="T58" s="10"/>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-      <c r="Y58" s="10"/>
-      <c r="Z58" s="10"/>
-      <c r="AA58" s="10"/>
-      <c r="AB58" s="10"/>
-    </row>
-    <row r="59" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-    </row>
-    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60" s="8" t="str">
+      <c r="L62" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
+      <c r="Z62" s="10"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="10"/>
+    </row>
+    <row r="63" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+    </row>
+    <row r="64" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8909,7 +9286,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E60" s="4" t="str">
+      <c r="E64" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -8954,53 +9331,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F60" s="9">
+      <c r="F64" s="9">
         <v>120</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G64" s="9">
         <v>84</v>
       </c>
-      <c r="H60" s="4" t="b">
+      <c r="H64" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I64" s="5">
         <v>46176</v>
       </c>
-      <c r="J60" s="4" t="b">
+      <c r="J64" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K60" s="17">
+      <c r="K64" s="17">
         <v>46176</v>
       </c>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
-      <c r="R60" s="10"/>
-      <c r="S60" s="10"/>
-      <c r="T60" s="10"/>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="10"/>
-      <c r="Y60" s="10"/>
-      <c r="Z60" s="10"/>
-      <c r="AA60" s="10"/>
-      <c r="AB60" s="10"/>
-    </row>
-    <row r="61" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D61" s="8" t="str">
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="10"/>
+      <c r="Y64" s="10"/>
+      <c r="Z64" s="10"/>
+      <c r="AA64" s="10"/>
+      <c r="AB64" s="10"/>
+    </row>
+    <row r="65" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9046,7 +9423,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E61" s="4" t="str">
+      <c r="E65" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9093,36 +9470,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F61" s="15">
+      <c r="F65" s="15">
         <v>165</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G65" s="15">
         <v>115</v>
       </c>
-      <c r="H61" s="4" t="b">
+      <c r="H65" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I65" s="5">
         <v>46176</v>
       </c>
-      <c r="J61" s="4" t="b">
+      <c r="J65" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K61" s="17">
+      <c r="K65" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D62" s="8" t="str">
+    <row r="66" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9168,7 +9545,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E62" s="4" t="str">
+      <c r="E66" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9215,36 +9592,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F62" s="15">
+      <c r="F66" s="15">
         <v>350</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G66" s="15">
         <v>245</v>
       </c>
-      <c r="H62" s="4" t="b">
+      <c r="H66" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I66" s="5">
         <v>46176</v>
       </c>
-      <c r="J62" s="4" t="b">
+      <c r="J66" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K62" s="17">
+      <c r="K66" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D63" s="8" t="str">
+    <row r="67" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9288,7 +9665,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E63" s="4" t="str">
+      <c r="E67" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9333,53 +9710,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F63" s="9">
+      <c r="F67" s="9">
         <v>120</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G67" s="9">
         <v>84</v>
       </c>
-      <c r="H63" s="4" t="b">
+      <c r="H67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I67" s="5">
         <v>46176</v>
       </c>
-      <c r="J63" s="4" t="b">
+      <c r="J67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K63" s="17">
+      <c r="K67" s="17">
         <v>46176</v>
       </c>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="10"/>
-      <c r="Z63" s="10"/>
-      <c r="AA63" s="10"/>
-      <c r="AB63" s="10"/>
-    </row>
-    <row r="64" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" s="8" t="str">
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="10"/>
+      <c r="X67" s="10"/>
+      <c r="Y67" s="10"/>
+      <c r="Z67" s="10"/>
+      <c r="AA67" s="10"/>
+      <c r="AB67" s="10"/>
+    </row>
+    <row r="68" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9425,7 +9802,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E64" s="4" t="str">
+      <c r="E68" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9472,36 +9849,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F64" s="15">
+      <c r="F68" s="15">
         <v>165</v>
       </c>
-      <c r="G64" s="15">
+      <c r="G68" s="15">
         <v>115</v>
       </c>
-      <c r="H64" s="4" t="b">
+      <c r="H68" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I68" s="5">
         <v>46176</v>
       </c>
-      <c r="J64" s="4" t="b">
+      <c r="J68" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K64" s="17">
+      <c r="K68" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65" s="8" t="str">
+    <row r="69" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9547,7 +9924,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E65" s="4" t="str">
+      <c r="E69" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9594,36 +9971,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F65" s="15">
+      <c r="F69" s="15">
         <v>350</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G69" s="15">
         <v>245</v>
       </c>
-      <c r="H65" s="4" t="b">
+      <c r="H69" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I69" s="5">
         <v>46176</v>
       </c>
-      <c r="J65" s="4" t="b">
+      <c r="J69" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K65" s="17">
+      <c r="K69" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D66" s="8" t="str">
+    <row r="70" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9667,7 +10044,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E66" s="4" t="str">
+      <c r="E70" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -9712,53 +10089,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F66" s="9">
+      <c r="F70" s="9">
         <v>120</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G70" s="9">
         <v>84</v>
       </c>
-      <c r="H66" s="4" t="b">
+      <c r="H70" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I70" s="5">
         <v>46176</v>
       </c>
-      <c r="J66" s="4" t="b">
+      <c r="J70" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K66" s="17">
+      <c r="K70" s="17">
         <v>46176</v>
       </c>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
-      <c r="R66" s="10"/>
-      <c r="S66" s="10"/>
-      <c r="T66" s="10"/>
-      <c r="U66" s="10"/>
-      <c r="V66" s="10"/>
-      <c r="W66" s="10"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="10"/>
-      <c r="Z66" s="10"/>
-      <c r="AA66" s="10"/>
-      <c r="AB66" s="10"/>
-    </row>
-    <row r="67" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="8" t="str">
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
+      <c r="AA70" s="10"/>
+      <c r="AB70" s="10"/>
+    </row>
+    <row r="71" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9804,7 +10181,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E67" s="4" t="str">
+      <c r="E71" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -9851,36 +10228,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F67" s="15">
+      <c r="F71" s="15">
         <v>165</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G71" s="15">
         <v>115</v>
       </c>
-      <c r="H67" s="4" t="b">
+      <c r="H71" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I71" s="5">
         <v>46176</v>
       </c>
-      <c r="J67" s="4" t="b">
+      <c r="J71" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K67" s="17">
+      <c r="K71" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D68" s="8" t="str">
+    <row r="72" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9926,7 +10303,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E68" s="4" t="str">
+      <c r="E72" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -9973,36 +10350,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F68" s="15">
+      <c r="F72" s="15">
         <v>350</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G72" s="15">
         <v>245</v>
       </c>
-      <c r="H68" s="4" t="b">
+      <c r="H72" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I72" s="5">
         <v>46176</v>
       </c>
-      <c r="J68" s="4" t="b">
+      <c r="J72" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K68" s="17">
+      <c r="K72" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D69" s="8" t="str">
+    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10046,7 +10423,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E69" s="4" t="str">
+      <c r="E73" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10091,53 +10468,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F69" s="9">
+      <c r="F73" s="9">
         <v>120</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G73" s="9">
         <v>84</v>
       </c>
-      <c r="H69" s="4" t="b">
+      <c r="H73" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I73" s="5">
         <v>46176</v>
       </c>
-      <c r="J69" s="4" t="b">
+      <c r="J73" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K69" s="17">
+      <c r="K73" s="17">
         <v>46176</v>
       </c>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
-      <c r="V69" s="10"/>
-      <c r="W69" s="10"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="10"/>
-      <c r="Z69" s="10"/>
-      <c r="AA69" s="10"/>
-      <c r="AB69" s="10"/>
-    </row>
-    <row r="70" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D70" s="8" t="str">
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="10"/>
+      <c r="Y73" s="10"/>
+      <c r="Z73" s="10"/>
+      <c r="AA73" s="10"/>
+      <c r="AB73" s="10"/>
+    </row>
+    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10183,7 +10560,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E70" s="4" t="str">
+      <c r="E74" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10230,36 +10607,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F70" s="15">
+      <c r="F74" s="15">
         <v>165</v>
       </c>
-      <c r="G70" s="15">
+      <c r="G74" s="15">
         <v>115</v>
       </c>
-      <c r="H70" s="4" t="b">
+      <c r="H74" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I74" s="5">
         <v>46176</v>
       </c>
-      <c r="J70" s="4" t="b">
+      <c r="J74" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K70" s="17">
+      <c r="K74" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D71" s="8" t="str">
+    <row r="75" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10305,7 +10682,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E71" s="4" t="str">
+      <c r="E75" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10352,36 +10729,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F71" s="15">
+      <c r="F75" s="15">
         <v>350</v>
       </c>
-      <c r="G71" s="15">
+      <c r="G75" s="15">
         <v>245</v>
       </c>
-      <c r="H71" s="4" t="b">
+      <c r="H75" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I75" s="5">
         <v>46176</v>
       </c>
-      <c r="J71" s="4" t="b">
+      <c r="J75" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K71" s="17">
+      <c r="K75" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="11" t="s">
+    <row r="76" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D72" s="8" t="str">
+      <c r="C76" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10425,7 +10802,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E72" s="4" t="str">
+      <c r="E76" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10470,53 +10847,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F72" s="9">
+      <c r="F76" s="9">
         <v>120</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G76" s="9">
         <v>84</v>
       </c>
-      <c r="H72" s="4" t="b">
+      <c r="H76" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I76" s="5">
         <v>46176</v>
       </c>
-      <c r="J72" s="4" t="b">
+      <c r="J76" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K72" s="17">
+      <c r="K76" s="17">
         <v>46176</v>
       </c>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
-      <c r="R72" s="10"/>
-      <c r="S72" s="10"/>
-      <c r="T72" s="10"/>
-      <c r="U72" s="10"/>
-      <c r="V72" s="10"/>
-      <c r="W72" s="10"/>
-      <c r="X72" s="10"/>
-      <c r="Y72" s="10"/>
-      <c r="Z72" s="10"/>
-      <c r="AA72" s="10"/>
-      <c r="AB72" s="10"/>
-    </row>
-    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D73" s="8" t="str">
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="10"/>
+      <c r="U76" s="10"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="10"/>
+      <c r="X76" s="10"/>
+      <c r="Y76" s="10"/>
+      <c r="Z76" s="10"/>
+      <c r="AA76" s="10"/>
+      <c r="AB76" s="10"/>
+    </row>
+    <row r="77" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10562,7 +10939,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E73" s="4" t="str">
+      <c r="E77" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10609,36 +10986,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F73" s="15">
+      <c r="F77" s="15">
         <v>165</v>
       </c>
-      <c r="G73" s="15">
+      <c r="G77" s="15">
         <v>115</v>
       </c>
-      <c r="H73" s="4" t="b">
+      <c r="H77" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I77" s="5">
         <v>46176</v>
       </c>
-      <c r="J73" s="4" t="b">
+      <c r="J77" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K73" s="17">
+      <c r="K77" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D74" s="8" t="str">
+    <row r="78" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10684,7 +11061,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E74" s="4" t="str">
+      <c r="E78" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -10731,36 +11108,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F74" s="15">
+      <c r="F78" s="15">
         <v>350</v>
       </c>
-      <c r="G74" s="15">
+      <c r="G78" s="15">
         <v>245</v>
       </c>
-      <c r="H74" s="4" t="b">
+      <c r="H78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I78" s="5">
         <v>46176</v>
       </c>
-      <c r="J74" s="4" t="b">
+      <c r="J78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K74" s="17">
+      <c r="K78" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D75" s="8" t="str">
+    <row r="79" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10804,7 +11181,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E75" s="4" t="str">
+      <c r="E79" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -10849,53 +11226,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F75" s="9">
+      <c r="F79" s="9">
         <v>120</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G79" s="9">
         <v>84</v>
       </c>
-      <c r="H75" s="4" t="b">
+      <c r="H79" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I79" s="5">
         <v>46176</v>
       </c>
-      <c r="J75" s="4" t="b">
+      <c r="J79" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K75" s="17">
+      <c r="K79" s="17">
         <v>46176</v>
       </c>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
-      <c r="O75" s="10"/>
-      <c r="P75" s="10"/>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
-      <c r="V75" s="10"/>
-      <c r="W75" s="10"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="10"/>
-      <c r="Z75" s="10"/>
-      <c r="AA75" s="10"/>
-      <c r="AB75" s="10"/>
-    </row>
-    <row r="76" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D76" s="8" t="str">
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
+      <c r="V79" s="10"/>
+      <c r="W79" s="10"/>
+      <c r="X79" s="10"/>
+      <c r="Y79" s="10"/>
+      <c r="Z79" s="10"/>
+      <c r="AA79" s="10"/>
+      <c r="AB79" s="10"/>
+    </row>
+    <row r="80" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10941,7 +11318,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E76" s="4" t="str">
+      <c r="E80" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -10988,36 +11365,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F76" s="15">
+      <c r="F80" s="15">
         <v>165</v>
       </c>
-      <c r="G76" s="15">
+      <c r="G80" s="15">
         <v>115</v>
       </c>
-      <c r="H76" s="4" t="b">
+      <c r="H80" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I76" s="5">
+      <c r="I80" s="5">
         <v>46176</v>
       </c>
-      <c r="J76" s="4" t="b">
+      <c r="J80" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K76" s="17">
+      <c r="K80" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D77" s="8" t="str">
+    <row r="81" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11063,7 +11440,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E77" s="4" t="str">
+      <c r="E81" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11110,36 +11487,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F77" s="15">
+      <c r="F81" s="15">
         <v>350</v>
       </c>
-      <c r="G77" s="15">
+      <c r="G81" s="15">
         <v>245</v>
       </c>
-      <c r="H77" s="4" t="b">
+      <c r="H81" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I77" s="5">
+      <c r="I81" s="5">
         <v>46176</v>
       </c>
-      <c r="J77" s="4" t="b">
+      <c r="J81" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K77" s="17">
+      <c r="K81" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="B78" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="D78" s="8" t="str">
+    <row r="82" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -11183,7 +11560,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E78" s="4" t="str">
+      <c r="E82" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -11228,53 +11605,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F78" s="9">
+      <c r="F82" s="9">
         <v>120</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G82" s="9">
         <v>84</v>
       </c>
-      <c r="H78" s="4" t="b">
+      <c r="H82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I78" s="5">
+      <c r="I82" s="5">
         <v>46176</v>
       </c>
-      <c r="J78" s="4" t="b">
+      <c r="J82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K78" s="17">
+      <c r="K82" s="17">
         <v>46176</v>
       </c>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="10"/>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="10"/>
-      <c r="R78" s="10"/>
-      <c r="S78" s="10"/>
-      <c r="T78" s="10"/>
-      <c r="U78" s="10"/>
-      <c r="V78" s="10"/>
-      <c r="W78" s="10"/>
-      <c r="X78" s="10"/>
-      <c r="Y78" s="10"/>
-      <c r="Z78" s="10"/>
-      <c r="AA78" s="10"/>
-      <c r="AB78" s="10"/>
-    </row>
-    <row r="79" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="8" t="str">
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
+      <c r="S82" s="10"/>
+      <c r="T82" s="10"/>
+      <c r="U82" s="10"/>
+      <c r="V82" s="10"/>
+      <c r="W82" s="10"/>
+      <c r="X82" s="10"/>
+      <c r="Y82" s="10"/>
+      <c r="Z82" s="10"/>
+      <c r="AA82" s="10"/>
+      <c r="AB82" s="10"/>
+    </row>
+    <row r="83" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11320,7 +11697,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E79" s="4" t="str">
+      <c r="E83" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11367,36 +11744,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F79" s="15">
+      <c r="F83" s="15">
         <v>165</v>
       </c>
-      <c r="G79" s="15">
+      <c r="G83" s="15">
         <v>115</v>
       </c>
-      <c r="H79" s="4" t="b">
+      <c r="H83" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I79" s="5">
+      <c r="I83" s="5">
         <v>46176</v>
       </c>
-      <c r="J79" s="4" t="b">
+      <c r="J83" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K79" s="17">
+      <c r="K83" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D80" s="8" t="str">
+    <row r="84" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11442,7 +11819,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E80" s="4" t="str">
+      <c r="E84" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11489,36 +11866,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F80" s="15">
+      <c r="F84" s="15">
         <v>350</v>
       </c>
-      <c r="G80" s="15">
+      <c r="G84" s="15">
         <v>245</v>
       </c>
-      <c r="H80" s="4" t="b">
+      <c r="H84" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I80" s="5">
+      <c r="I84" s="5">
         <v>46176</v>
       </c>
-      <c r="J80" s="4" t="b">
+      <c r="J84" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K80" s="17">
+      <c r="K84" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D81" s="8" t="str">
+    <row r="85" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D85" s="8" t="str">
         <f>Sheet2!$D$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -11562,7 +11939,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E81" s="4" t="str">
+      <c r="E85" s="4" t="str">
         <f>Sheet2!$A$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Basic Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Basic Assessment Package?**
@@ -11607,53 +11984,53 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F81" s="9">
+      <c r="F85" s="9">
         <v>120</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G85" s="9">
         <v>84</v>
       </c>
-      <c r="H81" s="4" t="b">
+      <c r="H85" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I81" s="5">
+      <c r="I85" s="5">
         <v>46176</v>
       </c>
-      <c r="J81" s="4" t="b">
+      <c r="J85" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K81" s="17">
+      <c r="K85" s="17">
         <v>46176</v>
       </c>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
-      <c r="N81" s="10"/>
-      <c r="O81" s="10"/>
-      <c r="P81" s="10"/>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
-      <c r="V81" s="10"/>
-      <c r="W81" s="10"/>
-      <c r="X81" s="10"/>
-      <c r="Y81" s="10"/>
-      <c r="Z81" s="10"/>
-      <c r="AA81" s="10"/>
-      <c r="AB81" s="10"/>
-    </row>
-    <row r="82" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D82" s="8" t="str">
+      <c r="L85" s="10"/>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
+      <c r="V85" s="10"/>
+      <c r="W85" s="10"/>
+      <c r="X85" s="10"/>
+      <c r="Y85" s="10"/>
+      <c r="Z85" s="10"/>
+      <c r="AA85" s="10"/>
+      <c r="AB85" s="10"/>
+    </row>
+    <row r="86" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="8" t="str">
         <f>Sheet2!$E$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11699,7 +12076,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E82" s="4" t="str">
+      <c r="E86" s="4" t="str">
         <f>Sheet2!$B$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Standard Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Standard Assessment Package?**
@@ -11746,36 +12123,36 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F82" s="15">
+      <c r="F86" s="15">
         <v>165</v>
       </c>
-      <c r="G82" s="15">
+      <c r="G86" s="15">
         <v>115</v>
       </c>
-      <c r="H82" s="4" t="b">
+      <c r="H86" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I82" s="5">
+      <c r="I86" s="5">
         <v>46176</v>
       </c>
-      <c r="J82" s="4" t="b">
+      <c r="J86" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K82" s="17">
+      <c r="K86" s="17">
         <v>46176</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="B83" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D83" s="8" t="str">
+    <row r="87" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="8" t="str">
         <f>Sheet2!$F$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11821,7 +12198,7 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="E83" s="4" t="str">
+      <c r="E87" s="4" t="str">
         <f>Sheet2!$C$2</f>
         <v xml:space="preserve">*Tinatamad ka ba, walang time, o nahihirapang gumawa ng TOS at  First Summative exam mo, KasaMath? Kuha ka na ng Premium Assessment Package habang naka-Early Bird Promo!*
 **Bakit perfect para sa’yo ang Premium Assessment Package?**
@@ -11868,40 +12245,24 @@
 Salamat sa pagsuporta sa **TeXMathPro, KasaMath**! Kung may tanong o suggestion ka, [kontakin mo lang ako](mailto:texmathpro@gmail.com). 
 </v>
       </c>
-      <c r="F83" s="15">
+      <c r="F87" s="15">
         <v>350</v>
       </c>
-      <c r="G83" s="15">
+      <c r="G87" s="15">
         <v>245</v>
       </c>
-      <c r="H83" s="4" t="b">
+      <c r="H87" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I83" s="5">
+      <c r="I87" s="5">
         <v>46176</v>
       </c>
-      <c r="J83" s="4" t="b">
+      <c r="J87" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="K83" s="17">
+      <c r="K87" s="17">
         <v>46176</v>
       </c>
-    </row>
-    <row r="84" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-    </row>
-    <row r="85" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-    </row>
-    <row r="86" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-    </row>
-    <row r="87" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
     </row>
     <row r="88" spans="1:28" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F88" s="19"/>
@@ -15490,6 +15851,22 @@
     <row r="984" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
       <c r="F984" s="19"/>
       <c r="G984" s="19"/>
+    </row>
+    <row r="985" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F985" s="19"/>
+      <c r="G985" s="19"/>
+    </row>
+    <row r="986" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F986" s="19"/>
+      <c r="G986" s="19"/>
+    </row>
+    <row r="987" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F987" s="19"/>
+      <c r="G987" s="19"/>
+    </row>
+    <row r="988" spans="6:7" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="F988" s="19"/>
+      <c r="G988" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15518,53 +15895,55 @@
     <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="C26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
     <hyperlink ref="C27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C32" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C39" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C41" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C42" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C43" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C44" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C45" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C49" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C50" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C51" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C52" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C53" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C54" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C55" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C56" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C57" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C58" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C60" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C61" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C62" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C63" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C64" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C65" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C67" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C69" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C70" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C71" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C72" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C73" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C74" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C75" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C76" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C77" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C78" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C79" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C80" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C81" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C82" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C83" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C30" r:id="rId70" xr:uid="{C3D8895E-36F9-C446-9032-98D1DBA560B2}"/>
-    <hyperlink ref="C36" r:id="rId71" xr:uid="{01D04C71-5B69-CD49-B99C-9F3396BA5C94}"/>
-    <hyperlink ref="C37" r:id="rId72" xr:uid="{993E0396-71F4-7543-B9D1-2323DD4B1A4A}"/>
+    <hyperlink ref="C44" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C47" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C48" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C49" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C53" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C54" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C55" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C56" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C57" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C58" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C59" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C60" r:id="rId39" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C62" r:id="rId40" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C64" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C65" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C66" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C67" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C68" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C69" r:id="rId46" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C70" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C71" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C72" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C73" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C74" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C75" r:id="rId52" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C76" r:id="rId53" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C77" r:id="rId54" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C78" r:id="rId55" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C79" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C80" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C81" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C82" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C83" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C84" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C85" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C86" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C87" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C34" r:id="rId65" xr:uid="{C3D8895E-36F9-C446-9032-98D1DBA560B2}"/>
+    <hyperlink ref="C40" r:id="rId66" xr:uid="{01D04C71-5B69-CD49-B99C-9F3396BA5C94}"/>
+    <hyperlink ref="C43" r:id="rId67" xr:uid="{993E0396-71F4-7543-B9D1-2323DD4B1A4A}"/>
+    <hyperlink ref="C61" r:id="rId68" xr:uid="{74D92F56-9F4B-D94E-B07F-70DC18555F3F}"/>
+    <hyperlink ref="C32" r:id="rId69" xr:uid="{6117C927-2422-A647-A376-30E6E68FCE95}"/>
+    <hyperlink ref="C38" r:id="rId70" xr:uid="{443F0D7B-AB73-DB4E-BCE7-81C6555F559E}"/>
+    <hyperlink ref="C41" r:id="rId71" xr:uid="{5704C940-F1D5-2544-BE71-99F3BDF45585}"/>
+    <hyperlink ref="C33" r:id="rId72" xr:uid="{ACAEF9A9-13E1-0348-A343-96345D8C6AFB}"/>
+    <hyperlink ref="C39" r:id="rId73" xr:uid="{B735B44B-B3F5-DE4A-9AFF-2EF89CC2A64F}"/>
+    <hyperlink ref="C42" r:id="rId74" xr:uid="{05A86DD3-ECAD-9D47-B04E-240F29894DDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15580,67 +15959,67 @@
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>147</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>239</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D6" s="24" t="str">
         <f>CONCATENATE("
@@ -15653,19 +16032,19 @@
     </row>
     <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>1</v>
@@ -15682,133 +16061,133 @@
     </row>
     <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="F10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="21" t="str">
-        <f t="shared" ref="G10:G13" si="0">IF($F10, CONCATENATE("- [", B$9, " Handouts for the ",$A10, "](", B10, ")"), "")</f>
+        <f>IF($F10, CONCATENATE("- [", B$9, " Handouts for the ",$A10, "](", B10, ")"), "")</f>
         <v>- [Grade 7 Handouts for the 1st Term](https://drive.google.com/file/d/150NUP_Nq2tev-Qn00VInZTAaPrUAssmQ/view?usp=drivesdk)</v>
       </c>
       <c r="H10" s="21" t="str">
-        <f t="shared" ref="H10:H12" si="1">IF(H$9,IF($F10, CONCATENATE("- [", C$9, " Handouts for the ",$A10, "](", C10, ")"), ""),"")</f>
+        <f t="shared" ref="H10:H12" si="0">IF(H$9,IF($F10, CONCATENATE("- [", C$9, " Handouts for the ",$A10, "](", C10, ")"), ""),"")</f>
         <v/>
       </c>
       <c r="I10" s="21" t="str">
-        <f t="shared" ref="I10:I12" si="2">IF($F10, CONCATENATE("- [", D$9, " Handouts for the ",$A10, "](", D10, ")"), "")</f>
+        <f t="shared" ref="I10:I12" si="1">IF($F10, CONCATENATE("- [", D$9, " Handouts for the ",$A10, "](", D10, ")"), "")</f>
         <v>- [Grade 9 Handouts for the 1st Term](https://drive.google.com/file/d/1x4fsJFRIZ1vsqPk6OXbzsGErE1XdDNJQ/view?usp=drivesdk)</v>
       </c>
       <c r="J10" s="21" t="str">
-        <f t="shared" ref="J10:J12" si="3">IF(H$9,IF($F10, CONCATENATE("- [", E$9, " Handouts for the ",$A10, "](", E10, ")"), ""),"")</f>
+        <f t="shared" ref="J10:J12" si="2">IF(H$9,IF($F10, CONCATENATE("- [", E$9, " Handouts for the ",$A10, "](", E10, ")"), ""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G11" s="21" t="str">
+        <f t="shared" ref="G10:G13" si="3">IF($F11, CONCATENATE("- [", B$9, " Handouts for the ",$A11, "](", B11, ")"), "")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="21" t="str">
+      <c r="I11" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I11" s="21" t="str">
+      <c r="J11" s="21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J11" s="21" t="str">
+    </row>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21" t="str">
+      <c r="H12" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="21" t="str">
+      <c r="I12" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I12" s="21" t="str">
+      <c r="J12" s="21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J12" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
     </row>
     <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="H13" s="21" t="str">
@@ -15826,216 +16205,230 @@
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D17" s="10" t="str">
         <f>CONCATENATE(_xlfn._LONGTEXT("- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
 - Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
-- Maaga kang makakapag-submit ng TOS sa head mo. "," 
+- Ready-to-print exam: sakto sa Budget of Work an","g covered topics  
+- Number of days: "))</f>
+        <v xml:space="preserve">- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
 - Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: "), Sheet1!Q29," days  
-- ", Sheet1!R29,_xlfn._LONGTEXT("-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadube","mrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*"))</f>
+- Number of days: </v>
+      </c>
+      <c r="E17" s="24" t="str">
+        <f>CONCATENATE(_xlfn._LONGTEXT("- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work an","g covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: "))</f>
+        <v xml:space="preserve">- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: </v>
+      </c>
+      <c r="F17" s="10" t="str">
+        <f>CONCATENATE(_xlfn._LONGTEXT("- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
+- Maganda at consistent ang formatting ng test questions at figures.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang p","wedeng covered
+- Maaga kang makakapag-submit ng TOS sa head mo.  
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50"))</f>
         <v>- Makakatipid ka sa oras kaya makakapaghabol pa ng lessons.  
 - Maganda at consistent ang formatting ng test questions at figures.  
-- Ready na ang answer key kaya mas madali at mabilis ang pagche-check.  
+- Ready na ang answer key kaya mas madali at mabilis ang pagche-check. 
+- Fully customizable exam: kahit anong topic ang pwedeng covered
 - Maaga kang makakapag-submit ng TOS sa head mo.  
-- Ready-to-print exam: sakto sa Budget of Work ang covered topics  
-- Table of Specifications (21st Century format)  
-- Number of days: 15 days  
-- 25-item Multiple Choice test with Answer Key  
-- Para sa teachers na nagmamadali  
-[![Sample TOS formatted using 21st Century Skills](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)](https://res.cloudinary.com/dadubemrv/image/upload/v1768351176/tv5zwilsnzrad6r2q6sw.png)
-*Sample TOS formatted using 21st Century Skills*</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>159</v>
+- Table of Specifications using the 21st Century format
+- Number of days: pwede kahit ilan
+- Number of items: kahit ilan basta maximum of 50</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D18" s="10"/>
-      <c r="F18" s="10" t="s">
-        <v>159</v>
-      </c>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D19" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
